--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="CharacterTable" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WorkSpeedTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CharacterLevelTable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -529,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A2:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
@@ -538,7 +539,6 @@
     <col width="59.625" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
@@ -2169,4 +2169,1446 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:D108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>캐릭터 레벨 (= TID)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>이 레벨에 도달하는 데 필요한 경험치 (직전 레벨에서 · Lv1은 0)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CharacterLevelTID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>RequiredExp</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>시작 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>누적 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>누적 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>누적 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>누적 53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>누적 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>누적 97</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>누적 126</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>누적 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>누적 203</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" t="n">
+        <v>51</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>누적 254</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>61</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>누적 315</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" t="n">
+        <v>74</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>누적 389</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>89</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>누적 478</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>106</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>누적 584</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>128</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>누적 712</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" t="n">
+        <v>154</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>누적 866</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>18</v>
+      </c>
+      <c r="C26" t="n">
+        <v>184</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>누적 1,050</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>19</v>
+      </c>
+      <c r="C27" t="n">
+        <v>221</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>누적 1,271</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>20</v>
+      </c>
+      <c r="C28" t="n">
+        <v>266</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>누적 1,537</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" t="n">
+        <v>319</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>누적 1,856</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" t="n">
+        <v>383</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>누적 2,239</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>23</v>
+      </c>
+      <c r="C31" t="n">
+        <v>460</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>누적 2,699</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>24</v>
+      </c>
+      <c r="C32" t="n">
+        <v>552</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>누적 3,251</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>25</v>
+      </c>
+      <c r="C33" t="n">
+        <v>662</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>누적 3,913</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>26</v>
+      </c>
+      <c r="C34" t="n">
+        <v>794</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>누적 4,707</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>27</v>
+      </c>
+      <c r="C35" t="n">
+        <v>953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>누적 5,660</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>28</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1144</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>누적 6,804</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>29</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>누적 8,177</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1648</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>누적 9,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>31</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>누적 11,803</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>32</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2373</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>누적 14,176</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>33</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2848</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>누적 17,024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>34</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3418</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>누적 20,442</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>35</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4101</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>누적 24,543</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>36</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4922</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>누적 29,465</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>37</v>
+      </c>
+      <c r="C45" t="n">
+        <v>5906</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>누적 35,371</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>38</v>
+      </c>
+      <c r="C46" t="n">
+        <v>7088</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>누적 42,459</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>39</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8505</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>누적 50,964</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>40</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10206</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>누적 61,170</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>41</v>
+      </c>
+      <c r="C49" t="n">
+        <v>12248</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>누적 73,418</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>42</v>
+      </c>
+      <c r="C50" t="n">
+        <v>14697</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>누적 88,115</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>43</v>
+      </c>
+      <c r="C51" t="n">
+        <v>17637</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>누적 105,752</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>44</v>
+      </c>
+      <c r="C52" t="n">
+        <v>21164</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>누적 126,916</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>45</v>
+      </c>
+      <c r="C53" t="n">
+        <v>25397</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>누적 152,313</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>46</v>
+      </c>
+      <c r="C54" t="n">
+        <v>30477</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>누적 182,790</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>47</v>
+      </c>
+      <c r="C55" t="n">
+        <v>36572</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>누적 219,362</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>48</v>
+      </c>
+      <c r="C56" t="n">
+        <v>43887</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>누적 263,249</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>49</v>
+      </c>
+      <c r="C57" t="n">
+        <v>52664</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>누적 315,913</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>50</v>
+      </c>
+      <c r="C58" t="n">
+        <v>63197</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>누적 379,110</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>51</v>
+      </c>
+      <c r="C59" t="n">
+        <v>75836</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>누적 454,946</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>52</v>
+      </c>
+      <c r="C60" t="n">
+        <v>91004</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>누적 545,950</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>53</v>
+      </c>
+      <c r="C61" t="n">
+        <v>109205</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>누적 655,155</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>54</v>
+      </c>
+      <c r="C62" t="n">
+        <v>131046</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>누적 786,201</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>55</v>
+      </c>
+      <c r="C63" t="n">
+        <v>157255</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>누적 943,456</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>56</v>
+      </c>
+      <c r="C64" t="n">
+        <v>188706</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>누적 1,132,162</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>57</v>
+      </c>
+      <c r="C65" t="n">
+        <v>226448</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>누적 1,358,610</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>58</v>
+      </c>
+      <c r="C66" t="n">
+        <v>271737</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>누적 1,630,347</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>59</v>
+      </c>
+      <c r="C67" t="n">
+        <v>326085</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>누적 1,956,432</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>60</v>
+      </c>
+      <c r="C68" t="n">
+        <v>391302</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>누적 2,347,734</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>61</v>
+      </c>
+      <c r="C69" t="n">
+        <v>469562</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>누적 2,817,296</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>62</v>
+      </c>
+      <c r="C70" t="n">
+        <v>563475</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>누적 3,380,771</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>63</v>
+      </c>
+      <c r="C71" t="n">
+        <v>676170</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>누적 4,056,941</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>64</v>
+      </c>
+      <c r="C72" t="n">
+        <v>811404</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>누적 4,868,345</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>65</v>
+      </c>
+      <c r="C73" t="n">
+        <v>973685</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>누적 5,842,030</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>66</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1168422</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>누적 7,010,452</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>67</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1402106</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>누적 8,412,558</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>68</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1682527</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>누적 10,095,085</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>69</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2019033</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>누적 12,114,118</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>70</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2422839</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>누적 14,536,957</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>71</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2907407</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>누적 17,444,364</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>72</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3488889</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>누적 20,933,253</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>73</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4186667</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>누적 25,119,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>74</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5024000</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>누적 30,143,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>75</v>
+      </c>
+      <c r="C83" t="n">
+        <v>6028801</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>누적 36,172,721</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>76</v>
+      </c>
+      <c r="C84" t="n">
+        <v>7234561</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>누적 43,407,282</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>77</v>
+      </c>
+      <c r="C85" t="n">
+        <v>8681473</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>누적 52,088,755</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>78</v>
+      </c>
+      <c r="C86" t="n">
+        <v>10417768</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>누적 62,506,523</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>79</v>
+      </c>
+      <c r="C87" t="n">
+        <v>12501322</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>누적 75,007,845</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>80</v>
+      </c>
+      <c r="C88" t="n">
+        <v>15001586</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>누적 90,009,431</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>81</v>
+      </c>
+      <c r="C89" t="n">
+        <v>18001903</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>누적 108,011,334</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>82</v>
+      </c>
+      <c r="C90" t="n">
+        <v>21602284</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>누적 129,613,618</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>83</v>
+      </c>
+      <c r="C91" t="n">
+        <v>25922741</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>누적 155,536,359</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>84</v>
+      </c>
+      <c r="C92" t="n">
+        <v>31107289</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>누적 186,643,648</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>85</v>
+      </c>
+      <c r="C93" t="n">
+        <v>37328747</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>누적 223,972,395</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>86</v>
+      </c>
+      <c r="C94" t="n">
+        <v>44794497</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>누적 268,766,892</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>87</v>
+      </c>
+      <c r="C95" t="n">
+        <v>53753396</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>누적 322,520,288</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>88</v>
+      </c>
+      <c r="C96" t="n">
+        <v>64504076</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>누적 387,024,364</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>89</v>
+      </c>
+      <c r="C97" t="n">
+        <v>77404891</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>누적 464,429,255</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>90</v>
+      </c>
+      <c r="C98" t="n">
+        <v>92885869</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>누적 557,315,124</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>91</v>
+      </c>
+      <c r="C99" t="n">
+        <v>111463043</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>누적 668,778,167</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>92</v>
+      </c>
+      <c r="C100" t="n">
+        <v>133755652</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>누적 802,533,819</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>93</v>
+      </c>
+      <c r="C101" t="n">
+        <v>160506782</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>누적 963,040,601</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>94</v>
+      </c>
+      <c r="C102" t="n">
+        <v>192608139</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>누적 1,155,648,740</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>95</v>
+      </c>
+      <c r="C103" t="n">
+        <v>231129767</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>누적 1,386,778,507</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>96</v>
+      </c>
+      <c r="C104" t="n">
+        <v>277355721</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>누적 1,664,134,228</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>97</v>
+      </c>
+      <c r="C105" t="n">
+        <v>332826865</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>누적 1,996,961,093</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>98</v>
+      </c>
+      <c r="C106" t="n">
+        <v>399392238</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>누적 2,396,353,331</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>99</v>
+      </c>
+      <c r="C107" t="n">
+        <v>479270685</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>누적 2,875,624,016</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>100</v>
+      </c>
+      <c r="C108" t="n">
+        <v>575124823</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>만렙. 누적 3,450,748,839 (Lv1 판정 3,450,748,839회)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -530,15 +530,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
     <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="32.25" bestFit="1" customWidth="1" min="4" max="8"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="59.625" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
@@ -585,7 +592,32 @@
           <t>사냥 적성(전투력)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>농사 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>낚시 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>채굴 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>벌목 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>사냥 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -642,6 +674,31 @@
           <t>a</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -690,6 +747,31 @@
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -710,6 +792,11 @@
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -726,6 +813,11 @@
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -741,7 +833,12 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -781,7 +878,32 @@
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>WorkSpeedTable.WorkSpeedTID</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>WorkSpeedTable.WorkSpeedTID</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>WorkSpeedTable.WorkSpeedTID</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>WorkSpeedTable.WorkSpeedTID</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>WorkSpeedTable.WorkSpeedTID</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="n"/>
@@ -825,7 +947,32 @@
           <t>Hunting</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>FarmingCap</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>FishingCap</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>MiningCap</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>LoggingCap</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>HuntingCap</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -860,7 +1007,22 @@
       <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>시작 지급. 전 산업 1 — 어떤 산업이든 시작할 수 있어야 한다</t>
         </is>
@@ -895,7 +1057,22 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>농사 담당</t>
         </is>
@@ -930,7 +1107,22 @@
       <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
@@ -965,7 +1157,22 @@
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>채굴 담당</t>
         </is>
@@ -1000,7 +1207,22 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
@@ -1035,7 +1257,22 @@
       <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1070,7 +1307,22 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>농사 입문</t>
         </is>
@@ -1105,7 +1357,22 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>낚시 입문</t>
         </is>
@@ -1140,7 +1407,22 @@
       <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>채굴 입문</t>
         </is>
@@ -1175,7 +1457,22 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>벌목 입문</t>
         </is>
@@ -1210,7 +1507,22 @@
       <c r="I20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>사냥 입문</t>
         </is>
@@ -1245,7 +1557,22 @@
       <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
@@ -1280,7 +1607,22 @@
       <c r="I22" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1315,7 +1657,22 @@
       <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
@@ -1350,7 +1707,22 @@
       <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
@@ -1385,7 +1757,22 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -1420,7 +1807,22 @@
       <c r="I26" t="n">
         <v>2</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>채굴 특화</t>
         </is>
@@ -1455,7 +1857,22 @@
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>벌목 특화</t>
         </is>
@@ -1490,7 +1907,22 @@
       <c r="I28" t="n">
         <v>5</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>사냥 특화</t>
         </is>
@@ -1525,7 +1957,22 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -1560,7 +2007,22 @@
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
@@ -1595,7 +2057,22 @@
       <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>채굴 정예</t>
         </is>
@@ -1630,7 +2107,22 @@
       <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>낚시 정예</t>
         </is>
@@ -1665,7 +2157,22 @@
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>농사 정예</t>
         </is>
@@ -1700,7 +2207,22 @@
       <c r="I34" t="n">
         <v>7</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>사냥 정예</t>
         </is>
@@ -1735,7 +2257,22 @@
       <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>벌목 정예</t>
         </is>
@@ -1770,7 +2307,22 @@
       <c r="I36" t="n">
         <v>2</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="n">
+        <v>9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>9</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>농사 최상위</t>
         </is>
@@ -1805,7 +2357,22 @@
       <c r="I37" t="n">
         <v>3</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>낚시 최상위</t>
         </is>
@@ -1840,7 +2407,22 @@
       <c r="I38" t="n">
         <v>2</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>9</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>채굴 최상위</t>
         </is>
@@ -1875,7 +2457,22 @@
       <c r="I39" t="n">
         <v>7</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
         </is>
@@ -2177,15 +2774,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D108"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
@@ -2204,6 +2802,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>이 레벨에 도달하면 주는 적성 포인트 (10의 배수 레벨만 1)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
       </c>
@@ -2229,6 +2832,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -2248,6 +2856,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -2264,7 +2877,10 @@
       <c r="C5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -2275,6 +2891,7 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -2284,7 +2901,8 @@
       </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2304,6 +2922,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>AptitudePoint</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
@@ -2315,7 +2938,10 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>시작 레벨</t>
         </is>
@@ -2328,7 +2954,10 @@
       <c r="C10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>누적 10</t>
         </is>
@@ -2341,7 +2970,10 @@
       <c r="C11" t="n">
         <v>12</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>누적 22</t>
         </is>
@@ -2354,7 +2986,10 @@
       <c r="C12" t="n">
         <v>14</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>누적 36</t>
         </is>
@@ -2367,7 +3002,10 @@
       <c r="C13" t="n">
         <v>17</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>누적 53</t>
         </is>
@@ -2380,7 +3018,10 @@
       <c r="C14" t="n">
         <v>20</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>누적 73</t>
         </is>
@@ -2393,7 +3034,10 @@
       <c r="C15" t="n">
         <v>24</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>누적 97</t>
         </is>
@@ -2406,7 +3050,10 @@
       <c r="C16" t="n">
         <v>29</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>누적 126</t>
         </is>
@@ -2419,7 +3066,10 @@
       <c r="C17" t="n">
         <v>35</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>누적 161</t>
         </is>
@@ -2432,7 +3082,10 @@
       <c r="C18" t="n">
         <v>42</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>누적 203</t>
         </is>
@@ -2445,7 +3098,10 @@
       <c r="C19" t="n">
         <v>51</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>누적 254</t>
         </is>
@@ -2458,7 +3114,10 @@
       <c r="C20" t="n">
         <v>61</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>누적 315</t>
         </is>
@@ -2471,7 +3130,10 @@
       <c r="C21" t="n">
         <v>74</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>누적 389</t>
         </is>
@@ -2484,7 +3146,10 @@
       <c r="C22" t="n">
         <v>89</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>누적 478</t>
         </is>
@@ -2497,7 +3162,10 @@
       <c r="C23" t="n">
         <v>106</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>누적 584</t>
         </is>
@@ -2510,7 +3178,10 @@
       <c r="C24" t="n">
         <v>128</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>누적 712</t>
         </is>
@@ -2523,7 +3194,10 @@
       <c r="C25" t="n">
         <v>154</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>누적 866</t>
         </is>
@@ -2536,7 +3210,10 @@
       <c r="C26" t="n">
         <v>184</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>누적 1,050</t>
         </is>
@@ -2549,7 +3226,10 @@
       <c r="C27" t="n">
         <v>221</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>누적 1,271</t>
         </is>
@@ -2562,7 +3242,10 @@
       <c r="C28" t="n">
         <v>266</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>누적 1,537</t>
         </is>
@@ -2575,7 +3258,10 @@
       <c r="C29" t="n">
         <v>319</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>누적 1,856</t>
         </is>
@@ -2588,7 +3274,10 @@
       <c r="C30" t="n">
         <v>383</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>누적 2,239</t>
         </is>
@@ -2601,7 +3290,10 @@
       <c r="C31" t="n">
         <v>460</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>누적 2,699</t>
         </is>
@@ -2614,7 +3306,10 @@
       <c r="C32" t="n">
         <v>552</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>누적 3,251</t>
         </is>
@@ -2627,7 +3322,10 @@
       <c r="C33" t="n">
         <v>662</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>누적 3,913</t>
         </is>
@@ -2640,7 +3338,10 @@
       <c r="C34" t="n">
         <v>794</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>누적 4,707</t>
         </is>
@@ -2653,7 +3354,10 @@
       <c r="C35" t="n">
         <v>953</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>누적 5,660</t>
         </is>
@@ -2666,7 +3370,10 @@
       <c r="C36" t="n">
         <v>1144</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>누적 6,804</t>
         </is>
@@ -2679,7 +3386,10 @@
       <c r="C37" t="n">
         <v>1373</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>누적 8,177</t>
         </is>
@@ -2692,7 +3402,10 @@
       <c r="C38" t="n">
         <v>1648</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>누적 9,825</t>
         </is>
@@ -2705,7 +3418,10 @@
       <c r="C39" t="n">
         <v>1978</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>누적 11,803</t>
         </is>
@@ -2718,7 +3434,10 @@
       <c r="C40" t="n">
         <v>2373</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>누적 14,176</t>
         </is>
@@ -2731,7 +3450,10 @@
       <c r="C41" t="n">
         <v>2848</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>누적 17,024</t>
         </is>
@@ -2744,7 +3466,10 @@
       <c r="C42" t="n">
         <v>3418</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>누적 20,442</t>
         </is>
@@ -2757,7 +3482,10 @@
       <c r="C43" t="n">
         <v>4101</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>누적 24,543</t>
         </is>
@@ -2770,7 +3498,10 @@
       <c r="C44" t="n">
         <v>4922</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>누적 29,465</t>
         </is>
@@ -2783,7 +3514,10 @@
       <c r="C45" t="n">
         <v>5906</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>누적 35,371</t>
         </is>
@@ -2796,7 +3530,10 @@
       <c r="C46" t="n">
         <v>7088</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>누적 42,459</t>
         </is>
@@ -2809,7 +3546,10 @@
       <c r="C47" t="n">
         <v>8505</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>누적 50,964</t>
         </is>
@@ -2822,7 +3562,10 @@
       <c r="C48" t="n">
         <v>10206</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>누적 61,170</t>
         </is>
@@ -2835,7 +3578,10 @@
       <c r="C49" t="n">
         <v>12248</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>누적 73,418</t>
         </is>
@@ -2848,7 +3594,10 @@
       <c r="C50" t="n">
         <v>14697</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>누적 88,115</t>
         </is>
@@ -2861,7 +3610,10 @@
       <c r="C51" t="n">
         <v>17637</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>누적 105,752</t>
         </is>
@@ -2874,7 +3626,10 @@
       <c r="C52" t="n">
         <v>21164</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>누적 126,916</t>
         </is>
@@ -2887,7 +3642,10 @@
       <c r="C53" t="n">
         <v>25397</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>누적 152,313</t>
         </is>
@@ -2900,7 +3658,10 @@
       <c r="C54" t="n">
         <v>30477</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>누적 182,790</t>
         </is>
@@ -2913,7 +3674,10 @@
       <c r="C55" t="n">
         <v>36572</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>누적 219,362</t>
         </is>
@@ -2926,7 +3690,10 @@
       <c r="C56" t="n">
         <v>43887</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>누적 263,249</t>
         </is>
@@ -2939,7 +3706,10 @@
       <c r="C57" t="n">
         <v>52664</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>누적 315,913</t>
         </is>
@@ -2952,7 +3722,10 @@
       <c r="C58" t="n">
         <v>63197</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>누적 379,110</t>
         </is>
@@ -2965,7 +3738,10 @@
       <c r="C59" t="n">
         <v>75836</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>누적 454,946</t>
         </is>
@@ -2978,7 +3754,10 @@
       <c r="C60" t="n">
         <v>91004</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>누적 545,950</t>
         </is>
@@ -2991,7 +3770,10 @@
       <c r="C61" t="n">
         <v>109205</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>누적 655,155</t>
         </is>
@@ -3004,7 +3786,10 @@
       <c r="C62" t="n">
         <v>131046</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>누적 786,201</t>
         </is>
@@ -3017,7 +3802,10 @@
       <c r="C63" t="n">
         <v>157255</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>누적 943,456</t>
         </is>
@@ -3030,7 +3818,10 @@
       <c r="C64" t="n">
         <v>188706</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>누적 1,132,162</t>
         </is>
@@ -3043,7 +3834,10 @@
       <c r="C65" t="n">
         <v>226448</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>누적 1,358,610</t>
         </is>
@@ -3056,7 +3850,10 @@
       <c r="C66" t="n">
         <v>271737</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>누적 1,630,347</t>
         </is>
@@ -3069,7 +3866,10 @@
       <c r="C67" t="n">
         <v>326085</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>누적 1,956,432</t>
         </is>
@@ -3082,7 +3882,10 @@
       <c r="C68" t="n">
         <v>391302</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>누적 2,347,734</t>
         </is>
@@ -3095,7 +3898,10 @@
       <c r="C69" t="n">
         <v>469562</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>누적 2,817,296</t>
         </is>
@@ -3108,7 +3914,10 @@
       <c r="C70" t="n">
         <v>563475</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>누적 3,380,771</t>
         </is>
@@ -3121,7 +3930,10 @@
       <c r="C71" t="n">
         <v>676170</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>누적 4,056,941</t>
         </is>
@@ -3134,7 +3946,10 @@
       <c r="C72" t="n">
         <v>811404</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>누적 4,868,345</t>
         </is>
@@ -3147,7 +3962,10 @@
       <c r="C73" t="n">
         <v>973685</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>누적 5,842,030</t>
         </is>
@@ -3160,7 +3978,10 @@
       <c r="C74" t="n">
         <v>1168422</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>누적 7,010,452</t>
         </is>
@@ -3173,7 +3994,10 @@
       <c r="C75" t="n">
         <v>1402106</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>누적 8,412,558</t>
         </is>
@@ -3186,7 +4010,10 @@
       <c r="C76" t="n">
         <v>1682527</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>누적 10,095,085</t>
         </is>
@@ -3199,7 +4026,10 @@
       <c r="C77" t="n">
         <v>2019033</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>누적 12,114,118</t>
         </is>
@@ -3212,7 +4042,10 @@
       <c r="C78" t="n">
         <v>2422839</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>누적 14,536,957</t>
         </is>
@@ -3225,7 +4058,10 @@
       <c r="C79" t="n">
         <v>2907407</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>누적 17,444,364</t>
         </is>
@@ -3238,7 +4074,10 @@
       <c r="C80" t="n">
         <v>3488889</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>누적 20,933,253</t>
         </is>
@@ -3251,7 +4090,10 @@
       <c r="C81" t="n">
         <v>4186667</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>누적 25,119,920</t>
         </is>
@@ -3264,7 +4106,10 @@
       <c r="C82" t="n">
         <v>5024000</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>누적 30,143,920</t>
         </is>
@@ -3277,7 +4122,10 @@
       <c r="C83" t="n">
         <v>6028801</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>누적 36,172,721</t>
         </is>
@@ -3290,7 +4138,10 @@
       <c r="C84" t="n">
         <v>7234561</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>누적 43,407,282</t>
         </is>
@@ -3303,7 +4154,10 @@
       <c r="C85" t="n">
         <v>8681473</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>누적 52,088,755</t>
         </is>
@@ -3316,7 +4170,10 @@
       <c r="C86" t="n">
         <v>10417768</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>누적 62,506,523</t>
         </is>
@@ -3329,7 +4186,10 @@
       <c r="C87" t="n">
         <v>12501322</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>누적 75,007,845</t>
         </is>
@@ -3342,7 +4202,10 @@
       <c r="C88" t="n">
         <v>15001586</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t>누적 90,009,431</t>
         </is>
@@ -3355,7 +4218,10 @@
       <c r="C89" t="n">
         <v>18001903</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>누적 108,011,334</t>
         </is>
@@ -3368,7 +4234,10 @@
       <c r="C90" t="n">
         <v>21602284</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>누적 129,613,618</t>
         </is>
@@ -3381,7 +4250,10 @@
       <c r="C91" t="n">
         <v>25922741</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>누적 155,536,359</t>
         </is>
@@ -3394,7 +4266,10 @@
       <c r="C92" t="n">
         <v>31107289</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>누적 186,643,648</t>
         </is>
@@ -3407,7 +4282,10 @@
       <c r="C93" t="n">
         <v>37328747</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>누적 223,972,395</t>
         </is>
@@ -3420,7 +4298,10 @@
       <c r="C94" t="n">
         <v>44794497</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>누적 268,766,892</t>
         </is>
@@ -3433,7 +4314,10 @@
       <c r="C95" t="n">
         <v>53753396</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>누적 322,520,288</t>
         </is>
@@ -3446,7 +4330,10 @@
       <c r="C96" t="n">
         <v>64504076</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>누적 387,024,364</t>
         </is>
@@ -3459,7 +4346,10 @@
       <c r="C97" t="n">
         <v>77404891</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>누적 464,429,255</t>
         </is>
@@ -3472,7 +4362,10 @@
       <c r="C98" t="n">
         <v>92885869</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>누적 557,315,124</t>
         </is>
@@ -3485,7 +4378,10 @@
       <c r="C99" t="n">
         <v>111463043</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>누적 668,778,167</t>
         </is>
@@ -3498,7 +4394,10 @@
       <c r="C100" t="n">
         <v>133755652</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>누적 802,533,819</t>
         </is>
@@ -3511,7 +4410,10 @@
       <c r="C101" t="n">
         <v>160506782</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>누적 963,040,601</t>
         </is>
@@ -3524,7 +4426,10 @@
       <c r="C102" t="n">
         <v>192608139</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>누적 1,155,648,740</t>
         </is>
@@ -3537,7 +4442,10 @@
       <c r="C103" t="n">
         <v>231129767</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>누적 1,386,778,507</t>
         </is>
@@ -3550,7 +4458,10 @@
       <c r="C104" t="n">
         <v>277355721</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>누적 1,664,134,228</t>
         </is>
@@ -3563,7 +4474,10 @@
       <c r="C105" t="n">
         <v>332826865</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>누적 1,996,961,093</t>
         </is>
@@ -3576,7 +4490,10 @@
       <c r="C106" t="n">
         <v>399392238</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>누적 2,396,353,331</t>
         </is>
@@ -3589,7 +4506,10 @@
       <c r="C107" t="n">
         <v>479270685</v>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>누적 2,875,624,016</t>
         </is>
@@ -3602,7 +4522,10 @@
       <c r="C108" t="n">
         <v>575124823</v>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t>만렙. 누적 3,450,748,839 (Lv1 판정 3,450,748,839회)</t>
         </is>

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -75,8 +75,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +109,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -125,11 +138,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -164,6 +191,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -239,6 +293,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>레어도 (전역 등급)</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>사냥 적성(전투력)</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>농사 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>낚시 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>채굴 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>벌목 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>사냥 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>적성 등급 (= TID)</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>기본 작업속도 (천분율, 1000=기준 30초)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>캐릭터 레벨 (= TID)</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>이 레벨에 도달하는 데 필요한 경험치 (직전 레벨에서 · Lv1은 0)</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>이 레벨에 도달하면 주는 적성 포인트 (10의 배수 레벨만 1)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -525,7 +669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -533,16 +677,21 @@
   <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="32.25" bestFit="1" customWidth="1" min="4" max="8"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="59.625" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="15" bestFit="1" customWidth="1" min="4" max="8"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="13" max="13"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -552,74 +701,74 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>캐릭터 TID</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>레어도 (전역 등급)</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>레어도</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>농사 적성</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>낚시 적성</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>채굴 적성</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>벌목 적성</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>사냥 적성(전투력)</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>농사 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>낚시 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>채굴 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>벌목 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>사냥 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>사냥 적성</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>농사 상한</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>낚시 상한</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>채굴 상한</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="inlineStr">
+        <is>
+          <t>벌목 상한</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
+        <is>
+          <t>사냥 상한</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -629,72 +778,72 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -706,72 +855,72 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>eGlobalRarity</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -783,20 +932,20 @@
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="n"/>
+      <c r="M5" s="15" t="n"/>
+      <c r="N5" s="15" t="n"/>
+      <c r="O5" s="15" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -804,20 +953,20 @@
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="n"/>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="15" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -825,20 +974,20 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="15" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -850,1629 +999,1629 @@
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="O8" s="7" t="n"/>
+      <c r="O8" s="16" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>CharacterTID</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>GlobalRarity</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>FarmingCap</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>FishingCap</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>MiningCap</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t>LoggingCap</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="18" t="inlineStr">
         <is>
           <t>HuntingCap</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="19" t="n">
         <v>1001</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>램볼</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="E10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>시작 지급. 전 산업 1 — 어떤 산업이든 시작할 수 있어야 한다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="19" t="n">
         <v>1002</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>치키피</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="F11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>농사 담당</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="19" t="n">
         <v>1003</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>펭구렛</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="G12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="19" t="n">
         <v>1004</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>캐티바</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="E13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="H13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>채굴 담당</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="19" t="n">
         <v>1005</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>리프몽</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="E14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="19" t="n">
         <v>1006</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>폭스파크스</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="E15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="19" t="n">
         <v>1007</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>밀개비</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="E16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>농사 입문</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="19" t="n">
         <v>1008</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>물방개미</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="E17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>낚시 입문</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="19" t="n">
         <v>1009</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>두더삽</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="E18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>채굴 입문</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="19" t="n">
         <v>1010</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>톱니쥐</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="E19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>벌목 입문</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="19" t="n">
         <v>1011</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>살쾡이</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="E20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t>사냥 입문</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="19" t="n">
         <v>1012</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>갈대오리</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="G21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="19" t="n">
         <v>1013</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>뿔사슴이</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="E22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="20" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="19" t="n">
         <v>1014</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>솔방울곰</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="E23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="19" t="n">
         <v>1015</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>해달수</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="G24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="20" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="19" t="n">
         <v>1016</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>흙두꺼비</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="F25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="20" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
+      <c r="B26" s="19" t="n">
         <v>1017</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>광부오소리</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="E26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="H26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t>채굴 특화</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
+      <c r="B27" s="19" t="n">
         <v>1018</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>도끼늑대</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="E27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="I27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="20" t="inlineStr">
         <is>
           <t>벌목 특화</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
+      <c r="B28" s="19" t="n">
         <v>1019</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>창날매</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="E28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="20" t="inlineStr">
         <is>
           <t>사냥 특화</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="19" t="n">
         <v>1020</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>이삭토끼</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="F29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="20" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
+      <c r="B30" s="19" t="n">
         <v>1021</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>산호게</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="E30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="G30" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
+      <c r="B31" s="19" t="n">
         <v>1022</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>화산도롱뇽</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="E31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="H31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="20" t="inlineStr">
         <is>
           <t>채굴 정예</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
+      <c r="B32" s="19" t="n">
         <v>1023</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>파도고래</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="E32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="G32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="20" t="inlineStr">
         <is>
           <t>낚시 정예</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
+      <c r="B33" s="19" t="n">
         <v>1024</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>대지곰</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="F33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="20" t="inlineStr">
         <is>
           <t>농사 정예</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="19" t="n">
         <v>1025</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>강철사마귀</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="E34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
+      <c r="H34" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="20" t="inlineStr">
         <is>
           <t>사냥 정예</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
+      <c r="B35" s="19" t="n">
         <v>1026</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>거목정령</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="F35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="20" t="inlineStr">
         <is>
           <t>벌목 정예</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
+      <c r="B36" s="19" t="n">
         <v>1027</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>황금기린</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="F36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="I36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="I36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="20" t="inlineStr">
         <is>
           <t>농사 최상위</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
+      <c r="B37" s="19" t="n">
         <v>1028</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>심연이무기</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="E37" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="H37" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="20" t="inlineStr">
         <is>
           <t>낚시 최상위</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
+      <c r="B38" s="19" t="n">
         <v>1029</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>흑요석골렘</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="E38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="I38" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="20" t="inlineStr">
         <is>
           <t>채굴 최상위</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
+      <c r="B39" s="19" t="n">
         <v>1030</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>별빛드래곤</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="20" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
         </is>
@@ -2480,43 +2629,45 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20.625" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>적성 등급 (= TID)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>기본 작업속도 (천분율, 1000=기준 30초)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>적성 등급</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>작업속도(‰)</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -2526,17 +2677,17 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -2548,17 +2699,17 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2570,13 +2721,13 @@
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="B5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -2584,9 +2735,9 @@
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -2594,9 +2745,9 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2604,160 +2755,160 @@
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>WorkSpeedTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>BaseWorkSpeedPermille</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>배치 불가 — 이 산업을 다루지 못한다</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>기준. 30.0초</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="19" t="n">
         <v>1250</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>24.0초</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>20.0초</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>16.7초</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="19" t="n">
         <v>2100</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>14.3초</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="19" t="n">
         <v>2450</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>12.2초</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="19" t="n">
         <v>2800</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>10.7초</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="19" t="n">
         <v>3200</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>9.4초</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="19" t="n">
         <v>3600</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>8.3초</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>7.5초 (최대 4배)</t>
         </is>
@@ -2765,11 +2916,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2777,10 +2929,11 @@
   <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -2790,24 +2943,24 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>캐릭터 레벨 (= TID)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>이 레벨에 도달하는 데 필요한 경험치 (직전 레벨에서 · Lv1은 0)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>이 레벨에 도달하면 주는 적성 포인트 (10의 배수 레벨만 1)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>레벨</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>필요 경험치</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>적성 포인트</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -2817,22 +2970,22 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -2844,22 +2997,22 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2871,16 +3024,16 @@
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n"/>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -2888,10 +3041,10 @@
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -2899,10 +3052,10 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2910,1622 +3063,1622 @@
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>CharacterLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>RequiredExp</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>AptitudePoint</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="B9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>시작 레벨</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>누적 10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>누적 22</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>누적 36</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>누적 53</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>누적 73</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>누적 97</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="19" t="n">
         <v>29</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>누적 126</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>누적 161</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>누적 203</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="19" t="n">
         <v>51</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>누적 254</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="19" t="n">
         <v>61</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>누적 315</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="19" t="n">
         <v>74</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>누적 389</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="19" t="n">
         <v>89</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>누적 478</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="19" t="n">
         <v>106</v>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>누적 584</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="19" t="n">
         <v>128</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>누적 712</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="19" t="n">
         <v>154</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>누적 866</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
+      <c r="B26" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="19" t="n">
         <v>184</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>누적 1,050</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
+      <c r="B27" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="19" t="n">
         <v>221</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>누적 1,271</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
+      <c r="B28" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="19" t="n">
         <v>266</v>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>누적 1,537</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="19" t="n">
         <v>319</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>누적 1,856</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
+      <c r="B30" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="19" t="n">
         <v>383</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>누적 2,239</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
+      <c r="B31" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="19" t="n">
         <v>460</v>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>누적 2,699</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
+      <c r="B32" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="19" t="n">
         <v>552</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>누적 3,251</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
+      <c r="B33" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="19" t="n">
         <v>662</v>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>누적 3,913</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="19" t="n">
         <v>794</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>누적 4,707</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
+      <c r="B35" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="19" t="n">
         <v>953</v>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="D35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>누적 5,660</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
+      <c r="B36" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="19" t="n">
         <v>1144</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>누적 6,804</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
+      <c r="B37" s="19" t="n">
         <v>29</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="19" t="n">
         <v>1373</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>누적 8,177</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
+      <c r="B38" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="19" t="n">
         <v>1648</v>
       </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="D38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>누적 9,825</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
+      <c r="B39" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="19" t="n">
         <v>1978</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="D39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>누적 11,803</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
+      <c r="B40" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="19" t="n">
         <v>2373</v>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>누적 14,176</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
+      <c r="B41" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="19" t="n">
         <v>2848</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>누적 17,024</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
+      <c r="B42" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="19" t="n">
         <v>3418</v>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>누적 20,442</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
+      <c r="B43" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="19" t="n">
         <v>4101</v>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>누적 24,543</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
+      <c r="B44" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="19" t="n">
         <v>4922</v>
       </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="D44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>누적 29,465</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
+      <c r="B45" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="19" t="n">
         <v>5906</v>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="D45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>누적 35,371</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
+      <c r="B46" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="19" t="n">
         <v>7088</v>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="D46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>누적 42,459</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
+      <c r="B47" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="19" t="n">
         <v>8505</v>
       </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>누적 50,964</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
+      <c r="B48" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="19" t="n">
         <v>10206</v>
       </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="D48" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>누적 61,170</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
+      <c r="B49" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="19" t="n">
         <v>12248</v>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="D49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>누적 73,418</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
+      <c r="B50" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="19" t="n">
         <v>14697</v>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="D50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>누적 88,115</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
+      <c r="B51" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="19" t="n">
         <v>17637</v>
       </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>누적 105,752</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
+      <c r="B52" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="19" t="n">
         <v>21164</v>
       </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="D52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>누적 126,916</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
+      <c r="B53" s="19" t="n">
         <v>45</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="19" t="n">
         <v>25397</v>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="D53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
         <is>
           <t>누적 152,313</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
+      <c r="B54" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="19" t="n">
         <v>30477</v>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>누적 182,790</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
+      <c r="B55" s="19" t="n">
         <v>47</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="19" t="n">
         <v>36572</v>
       </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="D55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
         <is>
           <t>누적 219,362</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
+      <c r="B56" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="19" t="n">
         <v>43887</v>
       </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="D56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
         <is>
           <t>누적 263,249</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
+      <c r="B57" s="19" t="n">
         <v>49</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="19" t="n">
         <v>52664</v>
       </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="D57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
         <is>
           <t>누적 315,913</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="n">
+      <c r="B58" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="19" t="n">
         <v>63197</v>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="D58" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
         <is>
           <t>누적 379,110</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="n">
+      <c r="B59" s="19" t="n">
         <v>51</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="19" t="n">
         <v>75836</v>
       </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="D59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>누적 454,946</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
+      <c r="B60" s="19" t="n">
         <v>52</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="19" t="n">
         <v>91004</v>
       </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="D60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>누적 545,950</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="n">
+      <c r="B61" s="19" t="n">
         <v>53</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="19" t="n">
         <v>109205</v>
       </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="D61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>누적 655,155</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="n">
+      <c r="B62" s="19" t="n">
         <v>54</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="19" t="n">
         <v>131046</v>
       </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="D62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
         <is>
           <t>누적 786,201</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="n">
+      <c r="B63" s="19" t="n">
         <v>55</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="19" t="n">
         <v>157255</v>
       </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="D63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
         <is>
           <t>누적 943,456</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="n">
+      <c r="B64" s="19" t="n">
         <v>56</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="19" t="n">
         <v>188706</v>
       </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="D64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>누적 1,132,162</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="n">
+      <c r="B65" s="19" t="n">
         <v>57</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="19" t="n">
         <v>226448</v>
       </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="D65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>누적 1,358,610</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="n">
+      <c r="B66" s="19" t="n">
         <v>58</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="19" t="n">
         <v>271737</v>
       </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="D66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>누적 1,630,347</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="n">
+      <c r="B67" s="19" t="n">
         <v>59</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="19" t="n">
         <v>326085</v>
       </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="D67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>누적 1,956,432</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="n">
+      <c r="B68" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="19" t="n">
         <v>391302</v>
       </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="D68" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
         <is>
           <t>누적 2,347,734</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="n">
+      <c r="B69" s="19" t="n">
         <v>61</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="19" t="n">
         <v>469562</v>
       </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr">
+      <c r="D69" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="20" t="inlineStr">
         <is>
           <t>누적 2,817,296</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="n">
+      <c r="B70" s="19" t="n">
         <v>62</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="19" t="n">
         <v>563475</v>
       </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="D70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
         <is>
           <t>누적 3,380,771</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="n">
+      <c r="B71" s="19" t="n">
         <v>63</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="19" t="n">
         <v>676170</v>
       </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="D71" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="20" t="inlineStr">
         <is>
           <t>누적 4,056,941</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="n">
+      <c r="B72" s="19" t="n">
         <v>64</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="19" t="n">
         <v>811404</v>
       </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr">
+      <c r="D72" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
         <is>
           <t>누적 4,868,345</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="n">
+      <c r="B73" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="19" t="n">
         <v>973685</v>
       </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="D73" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
         <is>
           <t>누적 5,842,030</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="n">
+      <c r="B74" s="19" t="n">
         <v>66</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="19" t="n">
         <v>1168422</v>
       </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="D74" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
         <is>
           <t>누적 7,010,452</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="n">
+      <c r="B75" s="19" t="n">
         <v>67</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="19" t="n">
         <v>1402106</v>
       </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="D75" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
         <is>
           <t>누적 8,412,558</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="n">
+      <c r="B76" s="19" t="n">
         <v>68</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="19" t="n">
         <v>1682527</v>
       </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="D76" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
         <is>
           <t>누적 10,095,085</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="n">
+      <c r="B77" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="19" t="n">
         <v>2019033</v>
       </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr">
+      <c r="D77" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
         <is>
           <t>누적 12,114,118</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="n">
+      <c r="B78" s="19" t="n">
         <v>70</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="19" t="n">
         <v>2422839</v>
       </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="inlineStr">
+      <c r="D78" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
         <is>
           <t>누적 14,536,957</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="n">
+      <c r="B79" s="19" t="n">
         <v>71</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="19" t="n">
         <v>2907407</v>
       </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr">
+      <c r="D79" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
         <is>
           <t>누적 17,444,364</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="n">
+      <c r="B80" s="19" t="n">
         <v>72</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="19" t="n">
         <v>3488889</v>
       </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="D80" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
         <is>
           <t>누적 20,933,253</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="n">
+      <c r="B81" s="19" t="n">
         <v>73</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="19" t="n">
         <v>4186667</v>
       </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="D81" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="20" t="inlineStr">
         <is>
           <t>누적 25,119,920</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="n">
+      <c r="B82" s="19" t="n">
         <v>74</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="19" t="n">
         <v>5024000</v>
       </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="D82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
         <is>
           <t>누적 30,143,920</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="n">
+      <c r="B83" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="19" t="n">
         <v>6028801</v>
       </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr">
+      <c r="D83" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="20" t="inlineStr">
         <is>
           <t>누적 36,172,721</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="n">
+      <c r="B84" s="19" t="n">
         <v>76</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="19" t="n">
         <v>7234561</v>
       </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr">
+      <c r="D84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
         <is>
           <t>누적 43,407,282</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="n">
+      <c r="B85" s="19" t="n">
         <v>77</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="19" t="n">
         <v>8681473</v>
       </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="D85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="20" t="inlineStr">
         <is>
           <t>누적 52,088,755</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="n">
+      <c r="B86" s="19" t="n">
         <v>78</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="19" t="n">
         <v>10417768</v>
       </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="inlineStr">
+      <c r="D86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="20" t="inlineStr">
         <is>
           <t>누적 62,506,523</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="n">
+      <c r="B87" s="19" t="n">
         <v>79</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="19" t="n">
         <v>12501322</v>
       </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="D87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="20" t="inlineStr">
         <is>
           <t>누적 75,007,845</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="n">
+      <c r="B88" s="19" t="n">
         <v>80</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="19" t="n">
         <v>15001586</v>
       </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="inlineStr">
+      <c r="D88" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
         <is>
           <t>누적 90,009,431</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="n">
+      <c r="B89" s="19" t="n">
         <v>81</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="19" t="n">
         <v>18001903</v>
       </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="D89" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
         <is>
           <t>누적 108,011,334</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="n">
+      <c r="B90" s="19" t="n">
         <v>82</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="19" t="n">
         <v>21602284</v>
       </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr">
+      <c r="D90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
         <is>
           <t>누적 129,613,618</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="n">
+      <c r="B91" s="19" t="n">
         <v>83</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="19" t="n">
         <v>25922741</v>
       </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="D91" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
         <is>
           <t>누적 155,536,359</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="n">
+      <c r="B92" s="19" t="n">
         <v>84</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="19" t="n">
         <v>31107289</v>
       </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr">
+      <c r="D92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
         <is>
           <t>누적 186,643,648</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="n">
+      <c r="B93" s="19" t="n">
         <v>85</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="19" t="n">
         <v>37328747</v>
       </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="D93" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
         <is>
           <t>누적 223,972,395</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="n">
+      <c r="B94" s="19" t="n">
         <v>86</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="19" t="n">
         <v>44794497</v>
       </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="inlineStr">
+      <c r="D94" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
         <is>
           <t>누적 268,766,892</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="n">
+      <c r="B95" s="19" t="n">
         <v>87</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="19" t="n">
         <v>53753396</v>
       </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="D95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
         <is>
           <t>누적 322,520,288</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="n">
+      <c r="B96" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="19" t="n">
         <v>64504076</v>
       </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="inlineStr">
+      <c r="D96" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
         <is>
           <t>누적 387,024,364</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="n">
+      <c r="B97" s="19" t="n">
         <v>89</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="19" t="n">
         <v>77404891</v>
       </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="D97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
         <is>
           <t>누적 464,429,255</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="n">
+      <c r="B98" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="19" t="n">
         <v>92885869</v>
       </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="D98" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
         <is>
           <t>누적 557,315,124</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="n">
+      <c r="B99" s="19" t="n">
         <v>91</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="19" t="n">
         <v>111463043</v>
       </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="D99" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
         <is>
           <t>누적 668,778,167</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="n">
+      <c r="B100" s="19" t="n">
         <v>92</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="19" t="n">
         <v>133755652</v>
       </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="D100" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
         <is>
           <t>누적 802,533,819</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="n">
+      <c r="B101" s="19" t="n">
         <v>93</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="19" t="n">
         <v>160506782</v>
       </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="D101" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="20" t="inlineStr">
         <is>
           <t>누적 963,040,601</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="n">
+      <c r="B102" s="19" t="n">
         <v>94</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="19" t="n">
         <v>192608139</v>
       </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr">
+      <c r="D102" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
         <is>
           <t>누적 1,155,648,740</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="n">
+      <c r="B103" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="19" t="n">
         <v>231129767</v>
       </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="inlineStr">
+      <c r="D103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="20" t="inlineStr">
         <is>
           <t>누적 1,386,778,507</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="n">
+      <c r="B104" s="19" t="n">
         <v>96</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="19" t="n">
         <v>277355721</v>
       </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="inlineStr">
+      <c r="D104" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
         <is>
           <t>누적 1,664,134,228</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="n">
+      <c r="B105" s="19" t="n">
         <v>97</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="19" t="n">
         <v>332826865</v>
       </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr">
+      <c r="D105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="20" t="inlineStr">
         <is>
           <t>누적 1,996,961,093</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="n">
+      <c r="B106" s="19" t="n">
         <v>98</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="19" t="n">
         <v>399392238</v>
       </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr">
+      <c r="D106" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
         <is>
           <t>누적 2,396,353,331</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="n">
+      <c r="B107" s="19" t="n">
         <v>99</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="19" t="n">
         <v>479270685</v>
       </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr">
+      <c r="D107" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="20" t="inlineStr">
         <is>
           <t>누적 2,875,624,016</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="n">
+      <c r="B108" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="19" t="n">
         <v>575124823</v>
       </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="inlineStr">
+      <c r="D108" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
         <is>
           <t>만렙. 누적 3,450,748,839 (Lv1 판정 3,450,748,839회)</t>
         </is>
@@ -4533,5 +4686,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -83,8 +83,48 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -114,8 +154,13 @@
         <fgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -152,11 +197,12 @@
         <color indexed="64"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -218,6 +264,37 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -694,1934 +771,1980 @@
     <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+      <c r="F1" s="30" t="n"/>
+      <c r="G1" s="30" t="n"/>
+      <c r="H1" s="30" t="n"/>
+      <c r="I1" s="30" t="n"/>
+      <c r="J1" s="30" t="n"/>
+      <c r="K1" s="30" t="n"/>
+      <c r="L1" s="30" t="n"/>
+      <c r="M1" s="30" t="n"/>
+      <c r="N1" s="30" t="n"/>
+      <c r="O1" s="30" t="n"/>
+    </row>
     <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>캐릭터 TID</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>레어도</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>농사 적성</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>낚시 적성</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>채굴 적성</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>벌목 적성</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>사냥 적성</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="23" t="inlineStr">
         <is>
           <t>농사 상한</t>
         </is>
       </c>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>낚시 상한</t>
         </is>
       </c>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="L2" s="23" t="inlineStr">
         <is>
           <t>채굴 상한</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
+      <c r="M2" s="23" t="inlineStr">
         <is>
           <t>벌목 상한</t>
         </is>
       </c>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="N2" s="23" t="inlineStr">
         <is>
           <t>사냥 상한</t>
         </is>
       </c>
-      <c r="O2" s="13" t="inlineStr">
+      <c r="O2" s="23" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr">
+      <c r="L3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="M3" s="15" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="N3" s="15" t="inlineStr">
+      <c r="N3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="O3" s="15" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>eGlobalRarity</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="N4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O4" s="15" t="inlineStr">
+      <c r="O4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="15" t="n"/>
-      <c r="L5" s="15" t="n"/>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="24" t="n"/>
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="24" t="n"/>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="24" t="n"/>
+      <c r="O5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
-      <c r="K6" s="15" t="n"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="n"/>
+      <c r="M6" s="24" t="n"/>
+      <c r="N6" s="24" t="n"/>
+      <c r="O6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="15" t="n"/>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="inlineStr">
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="24" t="n"/>
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="24" t="n"/>
+      <c r="L7" s="24" t="n"/>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="n"/>
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="O8" s="16" t="n"/>
+      <c r="O8" s="25" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>CharacterTID</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>GlobalRarity</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>FarmingCap</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t>FishingCap</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="26" t="inlineStr">
         <is>
           <t>MiningCap</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t>LoggingCap</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="26" t="inlineStr">
         <is>
           <t>HuntingCap</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="n">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="27" t="n">
         <v>1001</v>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>램볼</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="E10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="28" t="inlineStr">
         <is>
           <t>시작 지급. 전 산업 1 — 어떤 산업이든 시작할 수 있어야 한다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="n">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="27" t="n">
         <v>1002</v>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>치키피</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="19" t="n">
+      <c r="F11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L11" s="19" t="n">
+      <c r="L11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M11" s="19" t="n">
+      <c r="M11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N11" s="19" t="n">
+      <c r="N11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O11" s="20" t="inlineStr">
+      <c r="O11" s="28" t="inlineStr">
         <is>
           <t>농사 담당</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="27" t="n">
         <v>1003</v>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>펭구렛</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="19" t="n">
+      <c r="E12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="19" t="n">
+      <c r="G12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="19" t="n">
+      <c r="L12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="M12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N12" s="19" t="n">
+      <c r="N12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="O12" s="28" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19" t="n">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="27" t="n">
         <v>1004</v>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>캐티바</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E13" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19" t="n">
+      <c r="E13" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="19" t="n">
+      <c r="H13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L13" s="19" t="n">
+      <c r="L13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="19" t="n">
+      <c r="M13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N13" s="19" t="n">
+      <c r="N13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="O13" s="28" t="inlineStr">
         <is>
           <t>채굴 담당</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19" t="n">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="27" t="n">
         <v>1005</v>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>리프몽</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="19" t="n">
+      <c r="E14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="19" t="n">
+      <c r="I14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="K14" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L14" s="19" t="n">
+      <c r="L14" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M14" s="19" t="n">
+      <c r="M14" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N14" s="19" t="n">
+      <c r="N14" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19" t="n">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="27" t="n">
         <v>1006</v>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>폭스파크스</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="19" t="n">
+      <c r="E15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="19" t="n">
+      <c r="L15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M15" s="19" t="n">
+      <c r="M15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N15" s="19" t="n">
+      <c r="N15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O15" s="20" t="inlineStr">
+      <c r="O15" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="19" t="n">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="27" t="n">
         <v>1007</v>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>밀개비</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
+      <c r="E16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" s="28" t="inlineStr">
         <is>
           <t>농사 입문</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="19" t="n">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="27" t="n">
         <v>1008</v>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>물방개미</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
+      <c r="E17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
         <is>
           <t>낚시 입문</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="n">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="27" t="n">
         <v>1009</v>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>두더삽</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" s="20" t="inlineStr">
+      <c r="E18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
         <is>
           <t>채굴 입문</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="n">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="27" t="n">
         <v>1010</v>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>톱니쥐</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="20" t="inlineStr">
+      <c r="E19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
         <is>
           <t>벌목 입문</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="19" t="n">
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="27" t="n">
         <v>1011</v>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>살쾡이</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" s="20" t="inlineStr">
+      <c r="E20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="28" t="inlineStr">
         <is>
           <t>사냥 입문</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="19" t="n">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="27" t="n">
         <v>1012</v>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>갈대오리</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19" t="n">
+      <c r="E21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="19" t="n">
+      <c r="G21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="K21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="19" t="n">
+      <c r="L21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="M21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N21" s="19" t="n">
+      <c r="N21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O21" s="20" t="inlineStr">
+      <c r="O21" s="28" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="19" t="n">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="27" t="n">
         <v>1013</v>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>뿔사슴이</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="19" t="n">
+      <c r="E22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="19" t="n">
+      <c r="J22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N22" s="19" t="n">
+      <c r="N22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="20" t="inlineStr">
+      <c r="O22" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="n">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="27" t="n">
         <v>1014</v>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>솔방울곰</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="19" t="n">
+      <c r="E23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="19" t="n">
+      <c r="I23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L23" s="19" t="n">
+      <c r="L23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="M23" s="19" t="n">
+      <c r="M23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N23" s="19" t="n">
+      <c r="N23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O23" s="20" t="inlineStr">
+      <c r="O23" s="28" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="19" t="n">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="27" t="n">
         <v>1015</v>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>해달수</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="19" t="n">
+      <c r="E24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="19" t="n">
+      <c r="G24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K24" s="19" t="n">
+      <c r="K24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L24" s="19" t="n">
+      <c r="L24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M24" s="19" t="n">
+      <c r="M24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N24" s="19" t="n">
+      <c r="N24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O24" s="20" t="inlineStr">
+      <c r="O24" s="28" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="19" t="n">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="27" t="n">
         <v>1016</v>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>흙두꺼비</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="19" t="n">
+      <c r="F25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="K25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L25" s="19" t="n">
+      <c r="L25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M25" s="19" t="n">
+      <c r="M25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N25" s="19" t="n">
+      <c r="N25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O25" s="20" t="inlineStr">
+      <c r="O25" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="n">
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="27" t="n">
         <v>1017</v>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>광부오소리</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="19" t="n">
+      <c r="E26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="19" t="n">
+      <c r="H26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M26" s="19" t="n">
+      <c r="M26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N26" s="19" t="n">
+      <c r="N26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O26" s="20" t="inlineStr">
+      <c r="O26" s="28" t="inlineStr">
         <is>
           <t>채굴 특화</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="19" t="n">
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="27" t="n">
         <v>1018</v>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>도끼늑대</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="19" t="n">
+      <c r="E27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="19" t="n">
+      <c r="I27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="K27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L27" s="19" t="n">
+      <c r="L27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M27" s="19" t="n">
+      <c r="M27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N27" s="19" t="n">
+      <c r="N27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O27" s="20" t="inlineStr">
+      <c r="O27" s="28" t="inlineStr">
         <is>
           <t>벌목 특화</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="19" t="n">
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="27" t="n">
         <v>1019</v>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>창날매</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="19" t="n">
+      <c r="E28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="19" t="n">
+      <c r="J28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="K28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L28" s="19" t="n">
+      <c r="L28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M28" s="19" t="n">
+      <c r="M28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N28" s="19" t="n">
+      <c r="N28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O28" s="20" t="inlineStr">
+      <c r="O28" s="28" t="inlineStr">
         <is>
           <t>사냥 특화</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="19" t="n">
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="27" t="n">
         <v>1020</v>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>이삭토끼</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="19" t="n">
+      <c r="F29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K29" s="19" t="n">
+      <c r="K29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L29" s="19" t="n">
+      <c r="L29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M29" s="19" t="n">
+      <c r="M29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N29" s="19" t="n">
+      <c r="N29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O29" s="20" t="inlineStr">
+      <c r="O29" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="19" t="n">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="27" t="n">
         <v>1021</v>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>산호게</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="19" t="n">
+      <c r="E30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="G30" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="19" t="n">
+      <c r="G30" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K30" s="19" t="n">
+      <c r="K30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L30" s="19" t="n">
+      <c r="L30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M30" s="19" t="n">
+      <c r="M30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="N30" s="19" t="n">
+      <c r="N30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O30" s="20" t="inlineStr">
+      <c r="O30" s="28" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="19" t="n">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="27" t="n">
         <v>1022</v>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>화산도롱뇽</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="19" t="n">
+      <c r="E31" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H31" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="19" t="n">
+      <c r="H31" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="K31" s="19" t="n">
+      <c r="K31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="L31" s="19" t="n">
+      <c r="L31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M31" s="19" t="n">
+      <c r="M31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="N31" s="19" t="n">
+      <c r="N31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O31" s="20" t="inlineStr">
+      <c r="O31" s="28" t="inlineStr">
         <is>
           <t>채굴 정예</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="19" t="n">
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="27" t="n">
         <v>1023</v>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>파도고래</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E32" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="19" t="n">
+      <c r="E32" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="19" t="n">
+      <c r="G32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="K32" s="19" t="n">
+      <c r="K32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="L32" s="19" t="n">
+      <c r="L32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M32" s="19" t="n">
+      <c r="M32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="N32" s="19" t="n">
+      <c r="N32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O32" s="20" t="inlineStr">
+      <c r="O32" s="28" t="inlineStr">
         <is>
           <t>낚시 정예</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="19" t="n">
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="27" t="n">
         <v>1024</v>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>대지곰</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E33" s="19" t="n">
+      <c r="E33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="19" t="n">
+      <c r="F33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="K33" s="19" t="n">
+      <c r="K33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="L33" s="19" t="n">
+      <c r="L33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M33" s="19" t="n">
+      <c r="M33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="N33" s="19" t="n">
+      <c r="N33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O33" s="20" t="inlineStr">
+      <c r="O33" s="28" t="inlineStr">
         <is>
           <t>농사 정예</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="19" t="n">
+      <c r="A34" s="30" t="n"/>
+      <c r="B34" s="27" t="n">
         <v>1025</v>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>강철사마귀</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="19" t="n">
+      <c r="E34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="19" t="n">
+      <c r="H34" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J34" s="19" t="n">
+      <c r="J34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="K34" s="19" t="n">
+      <c r="K34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="L34" s="19" t="n">
+      <c r="L34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M34" s="19" t="n">
+      <c r="M34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="N34" s="19" t="n">
+      <c r="N34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O34" s="20" t="inlineStr">
+      <c r="O34" s="28" t="inlineStr">
         <is>
           <t>사냥 정예</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="19" t="n">
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="27" t="n">
         <v>1026</v>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>거목정령</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="19" t="n">
+      <c r="F35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="19" t="n">
+      <c r="I35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="K35" s="19" t="n">
+      <c r="K35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="L35" s="19" t="n">
+      <c r="L35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M35" s="19" t="n">
+      <c r="M35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="N35" s="19" t="n">
+      <c r="N35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O35" s="20" t="inlineStr">
+      <c r="O35" s="28" t="inlineStr">
         <is>
           <t>벌목 정예</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="19" t="n">
+      <c r="A36" s="30" t="n"/>
+      <c r="B36" s="27" t="n">
         <v>1027</v>
       </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>황금기린</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="F36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="19" t="n">
+      <c r="F36" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="19" t="n">
+      <c r="I36" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="K36" s="19" t="n">
+      <c r="K36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="L36" s="19" t="n">
+      <c r="L36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M36" s="19" t="n">
+      <c r="M36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="N36" s="19" t="n">
+      <c r="N36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="O36" s="20" t="inlineStr">
+      <c r="O36" s="28" t="inlineStr">
         <is>
           <t>농사 최상위</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="19" t="n">
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="27" t="n">
         <v>1028</v>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>심연이무기</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="19" t="n">
+      <c r="E37" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="19" t="n">
+      <c r="H37" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="19" t="n">
+      <c r="J37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="K37" s="19" t="n">
+      <c r="K37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="L37" s="19" t="n">
+      <c r="L37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M37" s="19" t="n">
+      <c r="M37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="N37" s="19" t="n">
+      <c r="N37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="O37" s="20" t="inlineStr">
+      <c r="O37" s="28" t="inlineStr">
         <is>
           <t>낚시 최상위</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="19" t="n">
+      <c r="A38" s="30" t="n"/>
+      <c r="B38" s="27" t="n">
         <v>1029</v>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>흑요석골렘</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="28" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="19" t="n">
+      <c r="E38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="H38" s="19" t="n">
+      <c r="H38" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="I38" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="19" t="n">
+      <c r="I38" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="K38" s="19" t="n">
+      <c r="K38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="19" t="n">
+      <c r="L38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M38" s="19" t="n">
+      <c r="M38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="N38" s="19" t="n">
+      <c r="N38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="O38" s="20" t="inlineStr">
+      <c r="O38" s="28" t="inlineStr">
         <is>
           <t>채굴 최상위</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="19" t="n">
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="27" t="n">
         <v>1030</v>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>별빛드래곤</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="E39" s="19" t="n">
+      <c r="E39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F39" s="19" t="n">
+      <c r="F39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="19" t="n">
+      <c r="G39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H39" s="19" t="n">
+      <c r="H39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I39" s="19" t="n">
+      <c r="I39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J39" s="19" t="n">
+      <c r="J39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="19" t="n">
+      <c r="K39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="L39" s="19" t="n">
+      <c r="L39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M39" s="19" t="n">
+      <c r="M39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="N39" s="19" t="n">
+      <c r="N39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O39" s="20" t="inlineStr">
+      <c r="O39" s="28" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
         </is>
@@ -2648,267 +2771,283 @@
     <col width="37" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+    </row>
     <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>적성 등급</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>작업속도(‰)</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="n"/>
+      <c r="B5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>WorkSpeedTID</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>BaseWorkSpeedPermille</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>배치 불가 — 이 산업을 다루지 못한다</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="19" t="n">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>기준. 30.0초</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="19" t="n">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="27" t="n">
         <v>1250</v>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>24.0초</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>20.0초</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19" t="n">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="27" t="n">
         <v>1800</v>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>16.7초</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19" t="n">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="27" t="n">
         <v>2100</v>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>14.3초</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19" t="n">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="27" t="n">
         <v>2450</v>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>12.2초</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="19" t="n">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="27" t="n">
         <v>2800</v>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>10.7초</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="19" t="n">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="27" t="n">
         <v>3200</v>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>9.4초</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="n">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="27" t="n">
         <v>3600</v>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>8.3초</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="n">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>7.5초 (최대 4배)</t>
         </is>
@@ -2936,1749 +3075,1855 @@
     <col width="53" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+    </row>
     <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>레벨</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>필요 경험치</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>적성 포인트</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15" t="n"/>
+      <c r="B5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>CharacterLevelTID</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>RequiredExp</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>AptitudePoint</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>시작 레벨</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="19" t="n">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="D10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>누적 10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="n">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="D11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>누적 22</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="D12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>누적 36</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19" t="n">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="D13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="D13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>누적 53</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19" t="n">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="D14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>누적 73</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19" t="n">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="D15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="D15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>누적 97</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="19" t="n">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="D16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="D16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>누적 126</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="19" t="n">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="D17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="D17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>누적 161</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="n">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="D18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>누적 203</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="n">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="27" t="n">
         <v>51</v>
       </c>
-      <c r="D19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="D19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>누적 254</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="19" t="n">
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="27" t="n">
         <v>61</v>
       </c>
-      <c r="D20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="D20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>누적 315</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="19" t="n">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="27" t="n">
         <v>74</v>
       </c>
-      <c r="D21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="D21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>누적 389</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="19" t="n">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="27" t="n">
         <v>89</v>
       </c>
-      <c r="D22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="D22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>누적 478</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="n">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="27" t="n">
         <v>106</v>
       </c>
-      <c r="D23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="D23" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>누적 584</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="19" t="n">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="27" t="n">
         <v>128</v>
       </c>
-      <c r="D24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="D24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>누적 712</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="19" t="n">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="27" t="n">
         <v>154</v>
       </c>
-      <c r="D25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="D25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>누적 866</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="n">
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="27" t="n">
         <v>184</v>
       </c>
-      <c r="D26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="D26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>누적 1,050</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="19" t="n">
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="27" t="n">
         <v>221</v>
       </c>
-      <c r="D27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="D27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>누적 1,271</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="19" t="n">
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="27" t="n">
         <v>266</v>
       </c>
-      <c r="D28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="D28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>누적 1,537</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="19" t="n">
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="27" t="n">
         <v>319</v>
       </c>
-      <c r="D29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="D29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>누적 1,856</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="19" t="n">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="27" t="n">
         <v>383</v>
       </c>
-      <c r="D30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="D30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>누적 2,239</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="19" t="n">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="27" t="n">
         <v>460</v>
       </c>
-      <c r="D31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="D31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>누적 2,699</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="19" t="n">
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="27" t="n">
         <v>552</v>
       </c>
-      <c r="D32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="D32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>누적 3,251</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="19" t="n">
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="27" t="n">
         <v>662</v>
       </c>
-      <c r="D33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="D33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>누적 3,913</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="19" t="n">
+      <c r="A34" s="30" t="n"/>
+      <c r="B34" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="27" t="n">
         <v>794</v>
       </c>
-      <c r="D34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="D34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>누적 4,707</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="19" t="n">
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C35" s="27" t="n">
         <v>953</v>
       </c>
-      <c r="D35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="D35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>누적 5,660</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="19" t="n">
+      <c r="A36" s="30" t="n"/>
+      <c r="B36" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="27" t="n">
         <v>1144</v>
       </c>
-      <c r="D36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="D36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>누적 6,804</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="19" t="n">
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="27" t="n">
         <v>1373</v>
       </c>
-      <c r="D37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="D37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>누적 8,177</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="19" t="n">
+      <c r="A38" s="30" t="n"/>
+      <c r="B38" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="27" t="n">
         <v>1648</v>
       </c>
-      <c r="D38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="D38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>누적 9,825</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="19" t="n">
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C39" s="19" t="n">
+      <c r="C39" s="27" t="n">
         <v>1978</v>
       </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="D39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>누적 11,803</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="19" t="n">
+      <c r="A40" s="30" t="n"/>
+      <c r="B40" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="C40" s="19" t="n">
+      <c r="C40" s="27" t="n">
         <v>2373</v>
       </c>
-      <c r="D40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="D40" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>누적 14,176</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="19" t="n">
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="C41" s="19" t="n">
+      <c r="C41" s="27" t="n">
         <v>2848</v>
       </c>
-      <c r="D41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="D41" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
         <is>
           <t>누적 17,024</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="19" t="n">
+      <c r="A42" s="30" t="n"/>
+      <c r="B42" s="27" t="n">
         <v>34</v>
       </c>
-      <c r="C42" s="19" t="n">
+      <c r="C42" s="27" t="n">
         <v>3418</v>
       </c>
-      <c r="D42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="D42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>누적 20,442</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="19" t="n">
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="C43" s="19" t="n">
+      <c r="C43" s="27" t="n">
         <v>4101</v>
       </c>
-      <c r="D43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="D43" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
         <is>
           <t>누적 24,543</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="19" t="n">
+      <c r="A44" s="30" t="n"/>
+      <c r="B44" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="C44" s="19" t="n">
+      <c r="C44" s="27" t="n">
         <v>4922</v>
       </c>
-      <c r="D44" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="D44" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>누적 29,465</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="19" t="n">
+      <c r="A45" s="30" t="n"/>
+      <c r="B45" s="27" t="n">
         <v>37</v>
       </c>
-      <c r="C45" s="19" t="n">
+      <c r="C45" s="27" t="n">
         <v>5906</v>
       </c>
-      <c r="D45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="D45" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>누적 35,371</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="19" t="n">
+      <c r="A46" s="30" t="n"/>
+      <c r="B46" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="C46" s="19" t="n">
+      <c r="C46" s="27" t="n">
         <v>7088</v>
       </c>
-      <c r="D46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="D46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>누적 42,459</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="19" t="n">
+      <c r="A47" s="30" t="n"/>
+      <c r="B47" s="27" t="n">
         <v>39</v>
       </c>
-      <c r="C47" s="19" t="n">
+      <c r="C47" s="27" t="n">
         <v>8505</v>
       </c>
-      <c r="D47" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="D47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>누적 50,964</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="19" t="n">
+      <c r="A48" s="30" t="n"/>
+      <c r="B48" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="C48" s="19" t="n">
+      <c r="C48" s="27" t="n">
         <v>10206</v>
       </c>
-      <c r="D48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="D48" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
         <is>
           <t>누적 61,170</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="19" t="n">
+      <c r="A49" s="30" t="n"/>
+      <c r="B49" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="C49" s="19" t="n">
+      <c r="C49" s="27" t="n">
         <v>12248</v>
       </c>
-      <c r="D49" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="D49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>누적 73,418</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="19" t="n">
+      <c r="A50" s="30" t="n"/>
+      <c r="B50" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="C50" s="19" t="n">
+      <c r="C50" s="27" t="n">
         <v>14697</v>
       </c>
-      <c r="D50" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="D50" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
         <is>
           <t>누적 88,115</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="19" t="n">
+      <c r="A51" s="30" t="n"/>
+      <c r="B51" s="27" t="n">
         <v>43</v>
       </c>
-      <c r="C51" s="19" t="n">
+      <c r="C51" s="27" t="n">
         <v>17637</v>
       </c>
-      <c r="D51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="D51" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
         <is>
           <t>누적 105,752</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="19" t="n">
+      <c r="A52" s="30" t="n"/>
+      <c r="B52" s="27" t="n">
         <v>44</v>
       </c>
-      <c r="C52" s="19" t="n">
+      <c r="C52" s="27" t="n">
         <v>21164</v>
       </c>
-      <c r="D52" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="D52" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>누적 126,916</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="19" t="n">
+      <c r="A53" s="30" t="n"/>
+      <c r="B53" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="C53" s="19" t="n">
+      <c r="C53" s="27" t="n">
         <v>25397</v>
       </c>
-      <c r="D53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="D53" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
         <is>
           <t>누적 152,313</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="19" t="n">
+      <c r="A54" s="30" t="n"/>
+      <c r="B54" s="27" t="n">
         <v>46</v>
       </c>
-      <c r="C54" s="19" t="n">
+      <c r="C54" s="27" t="n">
         <v>30477</v>
       </c>
-      <c r="D54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="D54" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>누적 182,790</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="19" t="n">
+      <c r="A55" s="30" t="n"/>
+      <c r="B55" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="C55" s="19" t="n">
+      <c r="C55" s="27" t="n">
         <v>36572</v>
       </c>
-      <c r="D55" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="D55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
         <is>
           <t>누적 219,362</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="19" t="n">
+      <c r="A56" s="30" t="n"/>
+      <c r="B56" s="27" t="n">
         <v>48</v>
       </c>
-      <c r="C56" s="19" t="n">
+      <c r="C56" s="27" t="n">
         <v>43887</v>
       </c>
-      <c r="D56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="D56" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
         <is>
           <t>누적 263,249</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="19" t="n">
+      <c r="A57" s="30" t="n"/>
+      <c r="B57" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="C57" s="19" t="n">
+      <c r="C57" s="27" t="n">
         <v>52664</v>
       </c>
-      <c r="D57" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="D57" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
         <is>
           <t>누적 315,913</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="19" t="n">
+      <c r="A58" s="30" t="n"/>
+      <c r="B58" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="C58" s="19" t="n">
+      <c r="C58" s="27" t="n">
         <v>63197</v>
       </c>
-      <c r="D58" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="20" t="inlineStr">
+      <c r="D58" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="28" t="inlineStr">
         <is>
           <t>누적 379,110</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="19" t="n">
+      <c r="A59" s="30" t="n"/>
+      <c r="B59" s="27" t="n">
         <v>51</v>
       </c>
-      <c r="C59" s="19" t="n">
+      <c r="C59" s="27" t="n">
         <v>75836</v>
       </c>
-      <c r="D59" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="D59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="28" t="inlineStr">
         <is>
           <t>누적 454,946</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="19" t="n">
+      <c r="A60" s="30" t="n"/>
+      <c r="B60" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="C60" s="19" t="n">
+      <c r="C60" s="27" t="n">
         <v>91004</v>
       </c>
-      <c r="D60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="20" t="inlineStr">
+      <c r="D60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
         <is>
           <t>누적 545,950</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="19" t="n">
+      <c r="A61" s="30" t="n"/>
+      <c r="B61" s="27" t="n">
         <v>53</v>
       </c>
-      <c r="C61" s="19" t="n">
+      <c r="C61" s="27" t="n">
         <v>109205</v>
       </c>
-      <c r="D61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="D61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="28" t="inlineStr">
         <is>
           <t>누적 655,155</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="19" t="n">
+      <c r="A62" s="30" t="n"/>
+      <c r="B62" s="27" t="n">
         <v>54</v>
       </c>
-      <c r="C62" s="19" t="n">
+      <c r="C62" s="27" t="n">
         <v>131046</v>
       </c>
-      <c r="D62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="D62" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="28" t="inlineStr">
         <is>
           <t>누적 786,201</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="19" t="n">
+      <c r="A63" s="30" t="n"/>
+      <c r="B63" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="C63" s="19" t="n">
+      <c r="C63" s="27" t="n">
         <v>157255</v>
       </c>
-      <c r="D63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="D63" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
         <is>
           <t>누적 943,456</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="19" t="n">
+      <c r="A64" s="30" t="n"/>
+      <c r="B64" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="C64" s="19" t="n">
+      <c r="C64" s="27" t="n">
         <v>188706</v>
       </c>
-      <c r="D64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="D64" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
         <is>
           <t>누적 1,132,162</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="19" t="n">
+      <c r="A65" s="30" t="n"/>
+      <c r="B65" s="27" t="n">
         <v>57</v>
       </c>
-      <c r="C65" s="19" t="n">
+      <c r="C65" s="27" t="n">
         <v>226448</v>
       </c>
-      <c r="D65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="D65" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
         <is>
           <t>누적 1,358,610</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="19" t="n">
+      <c r="A66" s="30" t="n"/>
+      <c r="B66" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="C66" s="19" t="n">
+      <c r="C66" s="27" t="n">
         <v>271737</v>
       </c>
-      <c r="D66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="20" t="inlineStr">
+      <c r="D66" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="28" t="inlineStr">
         <is>
           <t>누적 1,630,347</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="19" t="n">
+      <c r="A67" s="30" t="n"/>
+      <c r="B67" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="C67" s="19" t="n">
+      <c r="C67" s="27" t="n">
         <v>326085</v>
       </c>
-      <c r="D67" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="D67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
         <is>
           <t>누적 1,956,432</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="19" t="n">
+      <c r="A68" s="30" t="n"/>
+      <c r="B68" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="C68" s="19" t="n">
+      <c r="C68" s="27" t="n">
         <v>391302</v>
       </c>
-      <c r="D68" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="20" t="inlineStr">
+      <c r="D68" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="28" t="inlineStr">
         <is>
           <t>누적 2,347,734</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="19" t="n">
+      <c r="A69" s="30" t="n"/>
+      <c r="B69" s="27" t="n">
         <v>61</v>
       </c>
-      <c r="C69" s="19" t="n">
+      <c r="C69" s="27" t="n">
         <v>469562</v>
       </c>
-      <c r="D69" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="D69" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
         <is>
           <t>누적 2,817,296</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="19" t="n">
+      <c r="A70" s="30" t="n"/>
+      <c r="B70" s="27" t="n">
         <v>62</v>
       </c>
-      <c r="C70" s="19" t="n">
+      <c r="C70" s="27" t="n">
         <v>563475</v>
       </c>
-      <c r="D70" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="D70" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="28" t="inlineStr">
         <is>
           <t>누적 3,380,771</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="19" t="n">
+      <c r="A71" s="30" t="n"/>
+      <c r="B71" s="27" t="n">
         <v>63</v>
       </c>
-      <c r="C71" s="19" t="n">
+      <c r="C71" s="27" t="n">
         <v>676170</v>
       </c>
-      <c r="D71" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="D71" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="28" t="inlineStr">
         <is>
           <t>누적 4,056,941</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="19" t="n">
+      <c r="A72" s="30" t="n"/>
+      <c r="B72" s="27" t="n">
         <v>64</v>
       </c>
-      <c r="C72" s="19" t="n">
+      <c r="C72" s="27" t="n">
         <v>811404</v>
       </c>
-      <c r="D72" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="20" t="inlineStr">
+      <c r="D72" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
         <is>
           <t>누적 4,868,345</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="19" t="n">
+      <c r="A73" s="30" t="n"/>
+      <c r="B73" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="C73" s="19" t="n">
+      <c r="C73" s="27" t="n">
         <v>973685</v>
       </c>
-      <c r="D73" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="D73" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
         <is>
           <t>누적 5,842,030</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="19" t="n">
+      <c r="A74" s="30" t="n"/>
+      <c r="B74" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="C74" s="19" t="n">
+      <c r="C74" s="27" t="n">
         <v>1168422</v>
       </c>
-      <c r="D74" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="20" t="inlineStr">
+      <c r="D74" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
         <is>
           <t>누적 7,010,452</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="19" t="n">
+      <c r="A75" s="30" t="n"/>
+      <c r="B75" s="27" t="n">
         <v>67</v>
       </c>
-      <c r="C75" s="19" t="n">
+      <c r="C75" s="27" t="n">
         <v>1402106</v>
       </c>
-      <c r="D75" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
+      <c r="D75" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
         <is>
           <t>누적 8,412,558</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="19" t="n">
+      <c r="A76" s="30" t="n"/>
+      <c r="B76" s="27" t="n">
         <v>68</v>
       </c>
-      <c r="C76" s="19" t="n">
+      <c r="C76" s="27" t="n">
         <v>1682527</v>
       </c>
-      <c r="D76" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="20" t="inlineStr">
+      <c r="D76" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="28" t="inlineStr">
         <is>
           <t>누적 10,095,085</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="19" t="n">
+      <c r="A77" s="30" t="n"/>
+      <c r="B77" s="27" t="n">
         <v>69</v>
       </c>
-      <c r="C77" s="19" t="n">
+      <c r="C77" s="27" t="n">
         <v>2019033</v>
       </c>
-      <c r="D77" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="D77" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
         <is>
           <t>누적 12,114,118</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="19" t="n">
+      <c r="A78" s="30" t="n"/>
+      <c r="B78" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="C78" s="19" t="n">
+      <c r="C78" s="27" t="n">
         <v>2422839</v>
       </c>
-      <c r="D78" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="20" t="inlineStr">
+      <c r="D78" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
         <is>
           <t>누적 14,536,957</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="19" t="n">
+      <c r="A79" s="30" t="n"/>
+      <c r="B79" s="27" t="n">
         <v>71</v>
       </c>
-      <c r="C79" s="19" t="n">
+      <c r="C79" s="27" t="n">
         <v>2907407</v>
       </c>
-      <c r="D79" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="D79" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
         <is>
           <t>누적 17,444,364</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="19" t="n">
+      <c r="A80" s="30" t="n"/>
+      <c r="B80" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="C80" s="19" t="n">
+      <c r="C80" s="27" t="n">
         <v>3488889</v>
       </c>
-      <c r="D80" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="D80" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
         <is>
           <t>누적 20,933,253</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="19" t="n">
+      <c r="A81" s="30" t="n"/>
+      <c r="B81" s="27" t="n">
         <v>73</v>
       </c>
-      <c r="C81" s="19" t="n">
+      <c r="C81" s="27" t="n">
         <v>4186667</v>
       </c>
-      <c r="D81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="D81" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
         <is>
           <t>누적 25,119,920</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="19" t="n">
+      <c r="A82" s="30" t="n"/>
+      <c r="B82" s="27" t="n">
         <v>74</v>
       </c>
-      <c r="C82" s="19" t="n">
+      <c r="C82" s="27" t="n">
         <v>5024000</v>
       </c>
-      <c r="D82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="D82" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
         <is>
           <t>누적 30,143,920</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="19" t="n">
+      <c r="A83" s="30" t="n"/>
+      <c r="B83" s="27" t="n">
         <v>75</v>
       </c>
-      <c r="C83" s="19" t="n">
+      <c r="C83" s="27" t="n">
         <v>6028801</v>
       </c>
-      <c r="D83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="20" t="inlineStr">
+      <c r="D83" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
         <is>
           <t>누적 36,172,721</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="19" t="n">
+      <c r="A84" s="30" t="n"/>
+      <c r="B84" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="C84" s="19" t="n">
+      <c r="C84" s="27" t="n">
         <v>7234561</v>
       </c>
-      <c r="D84" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="20" t="inlineStr">
+      <c r="D84" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="28" t="inlineStr">
         <is>
           <t>누적 43,407,282</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="19" t="n">
+      <c r="A85" s="30" t="n"/>
+      <c r="B85" s="27" t="n">
         <v>77</v>
       </c>
-      <c r="C85" s="19" t="n">
+      <c r="C85" s="27" t="n">
         <v>8681473</v>
       </c>
-      <c r="D85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="20" t="inlineStr">
+      <c r="D85" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="28" t="inlineStr">
         <is>
           <t>누적 52,088,755</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="19" t="n">
+      <c r="A86" s="30" t="n"/>
+      <c r="B86" s="27" t="n">
         <v>78</v>
       </c>
-      <c r="C86" s="19" t="n">
+      <c r="C86" s="27" t="n">
         <v>10417768</v>
       </c>
-      <c r="D86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="20" t="inlineStr">
+      <c r="D86" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
         <is>
           <t>누적 62,506,523</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="19" t="n">
+      <c r="A87" s="30" t="n"/>
+      <c r="B87" s="27" t="n">
         <v>79</v>
       </c>
-      <c r="C87" s="19" t="n">
+      <c r="C87" s="27" t="n">
         <v>12501322</v>
       </c>
-      <c r="D87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="D87" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="28" t="inlineStr">
         <is>
           <t>누적 75,007,845</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="19" t="n">
+      <c r="A88" s="30" t="n"/>
+      <c r="B88" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="C88" s="19" t="n">
+      <c r="C88" s="27" t="n">
         <v>15001586</v>
       </c>
-      <c r="D88" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="20" t="inlineStr">
+      <c r="D88" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="28" t="inlineStr">
         <is>
           <t>누적 90,009,431</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="19" t="n">
+      <c r="A89" s="30" t="n"/>
+      <c r="B89" s="27" t="n">
         <v>81</v>
       </c>
-      <c r="C89" s="19" t="n">
+      <c r="C89" s="27" t="n">
         <v>18001903</v>
       </c>
-      <c r="D89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="20" t="inlineStr">
+      <c r="D89" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="28" t="inlineStr">
         <is>
           <t>누적 108,011,334</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="19" t="n">
+      <c r="A90" s="30" t="n"/>
+      <c r="B90" s="27" t="n">
         <v>82</v>
       </c>
-      <c r="C90" s="19" t="n">
+      <c r="C90" s="27" t="n">
         <v>21602284</v>
       </c>
-      <c r="D90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="20" t="inlineStr">
+      <c r="D90" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="28" t="inlineStr">
         <is>
           <t>누적 129,613,618</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="19" t="n">
+      <c r="A91" s="30" t="n"/>
+      <c r="B91" s="27" t="n">
         <v>83</v>
       </c>
-      <c r="C91" s="19" t="n">
+      <c r="C91" s="27" t="n">
         <v>25922741</v>
       </c>
-      <c r="D91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="20" t="inlineStr">
+      <c r="D91" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="28" t="inlineStr">
         <is>
           <t>누적 155,536,359</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="19" t="n">
+      <c r="A92" s="30" t="n"/>
+      <c r="B92" s="27" t="n">
         <v>84</v>
       </c>
-      <c r="C92" s="19" t="n">
+      <c r="C92" s="27" t="n">
         <v>31107289</v>
       </c>
-      <c r="D92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="20" t="inlineStr">
+      <c r="D92" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="28" t="inlineStr">
         <is>
           <t>누적 186,643,648</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="19" t="n">
+      <c r="A93" s="30" t="n"/>
+      <c r="B93" s="27" t="n">
         <v>85</v>
       </c>
-      <c r="C93" s="19" t="n">
+      <c r="C93" s="27" t="n">
         <v>37328747</v>
       </c>
-      <c r="D93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
+      <c r="D93" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
         <is>
           <t>누적 223,972,395</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="19" t="n">
+      <c r="A94" s="30" t="n"/>
+      <c r="B94" s="27" t="n">
         <v>86</v>
       </c>
-      <c r="C94" s="19" t="n">
+      <c r="C94" s="27" t="n">
         <v>44794497</v>
       </c>
-      <c r="D94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="20" t="inlineStr">
+      <c r="D94" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="28" t="inlineStr">
         <is>
           <t>누적 268,766,892</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="19" t="n">
+      <c r="A95" s="30" t="n"/>
+      <c r="B95" s="27" t="n">
         <v>87</v>
       </c>
-      <c r="C95" s="19" t="n">
+      <c r="C95" s="27" t="n">
         <v>53753396</v>
       </c>
-      <c r="D95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="20" t="inlineStr">
+      <c r="D95" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="28" t="inlineStr">
         <is>
           <t>누적 322,520,288</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="19" t="n">
+      <c r="A96" s="30" t="n"/>
+      <c r="B96" s="27" t="n">
         <v>88</v>
       </c>
-      <c r="C96" s="19" t="n">
+      <c r="C96" s="27" t="n">
         <v>64504076</v>
       </c>
-      <c r="D96" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="20" t="inlineStr">
+      <c r="D96" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="28" t="inlineStr">
         <is>
           <t>누적 387,024,364</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="19" t="n">
+      <c r="A97" s="30" t="n"/>
+      <c r="B97" s="27" t="n">
         <v>89</v>
       </c>
-      <c r="C97" s="19" t="n">
+      <c r="C97" s="27" t="n">
         <v>77404891</v>
       </c>
-      <c r="D97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="D97" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
         <is>
           <t>누적 464,429,255</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="19" t="n">
+      <c r="A98" s="30" t="n"/>
+      <c r="B98" s="27" t="n">
         <v>90</v>
       </c>
-      <c r="C98" s="19" t="n">
+      <c r="C98" s="27" t="n">
         <v>92885869</v>
       </c>
-      <c r="D98" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="20" t="inlineStr">
+      <c r="D98" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="28" t="inlineStr">
         <is>
           <t>누적 557,315,124</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="19" t="n">
+      <c r="A99" s="30" t="n"/>
+      <c r="B99" s="27" t="n">
         <v>91</v>
       </c>
-      <c r="C99" s="19" t="n">
+      <c r="C99" s="27" t="n">
         <v>111463043</v>
       </c>
-      <c r="D99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="20" t="inlineStr">
+      <c r="D99" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="28" t="inlineStr">
         <is>
           <t>누적 668,778,167</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="19" t="n">
+      <c r="A100" s="30" t="n"/>
+      <c r="B100" s="27" t="n">
         <v>92</v>
       </c>
-      <c r="C100" s="19" t="n">
+      <c r="C100" s="27" t="n">
         <v>133755652</v>
       </c>
-      <c r="D100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="20" t="inlineStr">
+      <c r="D100" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="28" t="inlineStr">
         <is>
           <t>누적 802,533,819</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="19" t="n">
+      <c r="A101" s="30" t="n"/>
+      <c r="B101" s="27" t="n">
         <v>93</v>
       </c>
-      <c r="C101" s="19" t="n">
+      <c r="C101" s="27" t="n">
         <v>160506782</v>
       </c>
-      <c r="D101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="20" t="inlineStr">
+      <c r="D101" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="28" t="inlineStr">
         <is>
           <t>누적 963,040,601</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="19" t="n">
+      <c r="A102" s="30" t="n"/>
+      <c r="B102" s="27" t="n">
         <v>94</v>
       </c>
-      <c r="C102" s="19" t="n">
+      <c r="C102" s="27" t="n">
         <v>192608139</v>
       </c>
-      <c r="D102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="20" t="inlineStr">
+      <c r="D102" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="28" t="inlineStr">
         <is>
           <t>누적 1,155,648,740</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="19" t="n">
+      <c r="A103" s="30" t="n"/>
+      <c r="B103" s="27" t="n">
         <v>95</v>
       </c>
-      <c r="C103" s="19" t="n">
+      <c r="C103" s="27" t="n">
         <v>231129767</v>
       </c>
-      <c r="D103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="20" t="inlineStr">
+      <c r="D103" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="28" t="inlineStr">
         <is>
           <t>누적 1,386,778,507</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="19" t="n">
+      <c r="A104" s="30" t="n"/>
+      <c r="B104" s="27" t="n">
         <v>96</v>
       </c>
-      <c r="C104" s="19" t="n">
+      <c r="C104" s="27" t="n">
         <v>277355721</v>
       </c>
-      <c r="D104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="20" t="inlineStr">
+      <c r="D104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="28" t="inlineStr">
         <is>
           <t>누적 1,664,134,228</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="19" t="n">
+      <c r="A105" s="30" t="n"/>
+      <c r="B105" s="27" t="n">
         <v>97</v>
       </c>
-      <c r="C105" s="19" t="n">
+      <c r="C105" s="27" t="n">
         <v>332826865</v>
       </c>
-      <c r="D105" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="20" t="inlineStr">
+      <c r="D105" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="28" t="inlineStr">
         <is>
           <t>누적 1,996,961,093</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="19" t="n">
+      <c r="A106" s="30" t="n"/>
+      <c r="B106" s="27" t="n">
         <v>98</v>
       </c>
-      <c r="C106" s="19" t="n">
+      <c r="C106" s="27" t="n">
         <v>399392238</v>
       </c>
-      <c r="D106" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="20" t="inlineStr">
+      <c r="D106" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="28" t="inlineStr">
         <is>
           <t>누적 2,396,353,331</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="19" t="n">
+      <c r="A107" s="30" t="n"/>
+      <c r="B107" s="27" t="n">
         <v>99</v>
       </c>
-      <c r="C107" s="19" t="n">
+      <c r="C107" s="27" t="n">
         <v>479270685</v>
       </c>
-      <c r="D107" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="20" t="inlineStr">
+      <c r="D107" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="28" t="inlineStr">
         <is>
           <t>누적 2,875,624,016</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="19" t="n">
+      <c r="A108" s="30" t="n"/>
+      <c r="B108" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="C108" s="19" t="n">
+      <c r="C108" s="27" t="n">
         <v>575124823</v>
       </c>
-      <c r="D108" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="20" t="inlineStr">
+      <c r="D108" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="28" t="inlineStr">
         <is>
           <t>만렙. 누적 3,450,748,839 (Lv1 판정 3,450,748,839회)</t>
         </is>

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -123,6 +123,14 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -202,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -295,6 +303,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -746,12 +763,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -768,7 +785,8 @@
     <col width="29" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,6 +805,7 @@
       <c r="M1" s="30" t="n"/>
       <c r="N1" s="30" t="n"/>
       <c r="O1" s="30" t="n"/>
+      <c r="P1" s="30" t="n"/>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
@@ -859,7 +878,12 @@
           <t>사냥 상한</t>
         </is>
       </c>
-      <c r="O2" s="23" t="inlineStr">
+      <c r="O2" s="33" t="inlineStr">
+        <is>
+          <t>기본 가격</t>
+        </is>
+      </c>
+      <c r="P2" s="23" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -936,7 +960,12 @@
           <t>a</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="P3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -1013,7 +1042,12 @@
           <t>int</t>
         </is>
       </c>
-      <c r="O4" s="24" t="inlineStr">
+      <c r="O4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1038,7 +1072,10 @@
       <c r="L5" s="24" t="n"/>
       <c r="M5" s="24" t="n"/>
       <c r="N5" s="24" t="n"/>
-      <c r="O5" s="24" t="n"/>
+      <c r="O5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -1059,7 +1096,8 @@
       <c r="L6" s="24" t="n"/>
       <c r="M6" s="24" t="n"/>
       <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n"/>
+      <c r="O6" s="34" t="n"/>
+      <c r="P6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -1080,7 +1118,8 @@
       <c r="L7" s="24" t="n"/>
       <c r="M7" s="24" t="n"/>
       <c r="N7" s="24" t="n"/>
-      <c r="O7" s="24" t="inlineStr">
+      <c r="O7" s="34" t="n"/>
+      <c r="P7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1145,7 +1184,8 @@
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="O8" s="25" t="n"/>
+      <c r="O8" s="34" t="n"/>
+      <c r="P8" s="25" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="32" t="n"/>
@@ -1214,7 +1254,12 @@
           <t>HuntingCap</t>
         </is>
       </c>
-      <c r="O9" s="26" t="inlineStr">
+      <c r="O9" s="35" t="inlineStr">
+        <is>
+          <t>BasePrice</t>
+        </is>
+      </c>
+      <c r="P9" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1265,7 +1310,10 @@
       <c r="N10" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="O10" s="28" t="inlineStr">
+      <c r="O10" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" s="28" t="inlineStr">
         <is>
           <t>시작 지급. 전 산업 1 — 어떤 산업이든 시작할 수 있어야 한다</t>
         </is>
@@ -1316,7 +1364,10 @@
       <c r="N11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O11" s="28" t="inlineStr">
+      <c r="O11" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P11" s="28" t="inlineStr">
         <is>
           <t>농사 담당</t>
         </is>
@@ -1367,7 +1418,10 @@
       <c r="N12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="28" t="inlineStr">
+      <c r="O12" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P12" s="28" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
@@ -1418,7 +1472,10 @@
       <c r="N13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O13" s="28" t="inlineStr">
+      <c r="O13" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P13" s="28" t="inlineStr">
         <is>
           <t>채굴 담당</t>
         </is>
@@ -1469,7 +1526,10 @@
       <c r="N14" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O14" s="28" t="inlineStr">
+      <c r="O14" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P14" s="28" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
@@ -1520,7 +1580,10 @@
       <c r="N15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O15" s="28" t="inlineStr">
+      <c r="O15" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1571,7 +1634,10 @@
       <c r="N16" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="O16" s="28" t="inlineStr">
+      <c r="O16" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P16" s="28" t="inlineStr">
         <is>
           <t>농사 입문</t>
         </is>
@@ -1622,7 +1688,10 @@
       <c r="N17" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="O17" s="28" t="inlineStr">
+      <c r="O17" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P17" s="28" t="inlineStr">
         <is>
           <t>낚시 입문</t>
         </is>
@@ -1673,7 +1742,10 @@
       <c r="N18" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="O18" s="28" t="inlineStr">
+      <c r="O18" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P18" s="28" t="inlineStr">
         <is>
           <t>채굴 입문</t>
         </is>
@@ -1724,7 +1796,10 @@
       <c r="N19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="O19" s="28" t="inlineStr">
+      <c r="O19" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P19" s="28" t="inlineStr">
         <is>
           <t>벌목 입문</t>
         </is>
@@ -1775,7 +1850,10 @@
       <c r="N20" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="O20" s="28" t="inlineStr">
+      <c r="O20" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P20" s="28" t="inlineStr">
         <is>
           <t>사냥 입문</t>
         </is>
@@ -1826,7 +1904,10 @@
       <c r="N21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O21" s="28" t="inlineStr">
+      <c r="O21" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="28" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
@@ -1877,7 +1958,10 @@
       <c r="N22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="28" t="inlineStr">
+      <c r="O22" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P22" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1928,7 +2012,10 @@
       <c r="N23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="O23" s="28" t="inlineStr">
+      <c r="O23" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P23" s="28" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
@@ -1979,7 +2066,10 @@
       <c r="N24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O24" s="28" t="inlineStr">
+      <c r="O24" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P24" s="28" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
@@ -2030,7 +2120,10 @@
       <c r="N25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O25" s="28" t="inlineStr">
+      <c r="O25" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P25" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -2081,7 +2174,10 @@
       <c r="N26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O26" s="28" t="inlineStr">
+      <c r="O26" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P26" s="28" t="inlineStr">
         <is>
           <t>채굴 특화</t>
         </is>
@@ -2132,7 +2228,10 @@
       <c r="N27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O27" s="28" t="inlineStr">
+      <c r="O27" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P27" s="28" t="inlineStr">
         <is>
           <t>벌목 특화</t>
         </is>
@@ -2183,7 +2282,10 @@
       <c r="N28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O28" s="28" t="inlineStr">
+      <c r="O28" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P28" s="28" t="inlineStr">
         <is>
           <t>사냥 특화</t>
         </is>
@@ -2234,7 +2336,10 @@
       <c r="N29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O29" s="28" t="inlineStr">
+      <c r="O29" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P29" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -2285,7 +2390,10 @@
       <c r="N30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="O30" s="28" t="inlineStr">
+      <c r="O30" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="P30" s="28" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
@@ -2336,7 +2444,10 @@
       <c r="N31" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O31" s="28" t="inlineStr">
+      <c r="O31" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="P31" s="28" t="inlineStr">
         <is>
           <t>채굴 정예</t>
         </is>
@@ -2387,7 +2498,10 @@
       <c r="N32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O32" s="28" t="inlineStr">
+      <c r="O32" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="P32" s="28" t="inlineStr">
         <is>
           <t>낚시 정예</t>
         </is>
@@ -2438,7 +2552,10 @@
       <c r="N33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O33" s="28" t="inlineStr">
+      <c r="O33" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="P33" s="28" t="inlineStr">
         <is>
           <t>농사 정예</t>
         </is>
@@ -2489,7 +2606,10 @@
       <c r="N34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O34" s="28" t="inlineStr">
+      <c r="O34" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="P34" s="28" t="inlineStr">
         <is>
           <t>사냥 정예</t>
         </is>
@@ -2540,7 +2660,10 @@
       <c r="N35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O35" s="28" t="inlineStr">
+      <c r="O35" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="P35" s="28" t="inlineStr">
         <is>
           <t>벌목 정예</t>
         </is>
@@ -2591,7 +2714,10 @@
       <c r="N36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="O36" s="28" t="inlineStr">
+      <c r="O36" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P36" s="28" t="inlineStr">
         <is>
           <t>농사 최상위</t>
         </is>
@@ -2642,7 +2768,10 @@
       <c r="N37" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="O37" s="28" t="inlineStr">
+      <c r="O37" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P37" s="28" t="inlineStr">
         <is>
           <t>낚시 최상위</t>
         </is>
@@ -2693,7 +2822,10 @@
       <c r="N38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="O38" s="28" t="inlineStr">
+      <c r="O38" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P38" s="28" t="inlineStr">
         <is>
           <t>채굴 최상위</t>
         </is>
@@ -2744,7 +2876,10 @@
       <c r="N39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="O39" s="28" t="inlineStr">
+      <c r="O39" s="27" t="n">
+        <v>4000</v>
+      </c>
+      <c r="P39" s="28" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
         </is>
@@ -2752,12 +2887,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3055,12 +3190,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4931,6 +5066,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -405,31 +405,6 @@
         <t>사냥 적성(전투력)</t>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0">
-      <text>
-        <t>농사 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
-      <text>
-        <t>낚시 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0">
-      <text>
-        <t>채굴 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0">
-      <text>
-        <t>벌목 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="0" shapeId="0">
-      <text>
-        <t>사냥 적성 상한 (적성 포인트로 오를 수 있는 최댓값 · 기본 적성 이상)</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -458,6 +433,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel-table-creator</author>
+    <author>T-003</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -470,9 +446,9 @@
         <t>이 레벨에 도달하는 데 필요한 경험치 (직전 레벨에서 · Lv1은 0)</t>
       </text>
     </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
+    <comment ref="D2" authorId="1" shapeId="0">
       <text>
-        <t>이 레벨에 도달하면 주는 적성 포인트 (10의 배수 레벨만 1)</t>
+        <t>이 레벨의 작업속도 가산 총량(천분율, 누적값). 장비·특성 가산과 합산된다 — Lv1 0 · 레벨당 +10(+1%)</t>
       </text>
     </comment>
   </commentList>
@@ -768,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="2"/>
@@ -780,8 +756,8 @@
     <col width="29" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
     <col width="29" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
@@ -801,11 +777,6 @@
       <c r="I1" s="30" t="n"/>
       <c r="J1" s="30" t="n"/>
       <c r="K1" s="30" t="n"/>
-      <c r="L1" s="30" t="n"/>
-      <c r="M1" s="30" t="n"/>
-      <c r="N1" s="30" t="n"/>
-      <c r="O1" s="30" t="n"/>
-      <c r="P1" s="30" t="n"/>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
@@ -853,37 +824,12 @@
           <t>사냥 적성</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
-        <is>
-          <t>농사 상한</t>
+      <c r="J2" s="33" t="inlineStr">
+        <is>
+          <t>기본 가격</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr">
-        <is>
-          <t>낚시 상한</t>
-        </is>
-      </c>
-      <c r="L2" s="23" t="inlineStr">
-        <is>
-          <t>채굴 상한</t>
-        </is>
-      </c>
-      <c r="M2" s="23" t="inlineStr">
-        <is>
-          <t>벌목 상한</t>
-        </is>
-      </c>
-      <c r="N2" s="23" t="inlineStr">
-        <is>
-          <t>사냥 상한</t>
-        </is>
-      </c>
-      <c r="O2" s="33" t="inlineStr">
-        <is>
-          <t>기본 가격</t>
-        </is>
-      </c>
-      <c r="P2" s="23" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -935,37 +881,12 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="34" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
       <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="L3" s="24" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="M3" s="24" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="N3" s="24" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="O3" s="34" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="P3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -1017,37 +938,12 @@
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
       <c r="K4" s="24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L4" s="24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M4" s="24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N4" s="24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O4" s="34" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="P4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1067,15 +963,10 @@
       <c r="G5" s="24" t="n"/>
       <c r="H5" s="24" t="n"/>
       <c r="I5" s="24" t="n"/>
-      <c r="J5" s="24" t="n"/>
+      <c r="J5" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="24" t="n"/>
-      <c r="L5" s="24" t="n"/>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="24" t="n"/>
-      <c r="O5" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -1091,13 +982,8 @@
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
       <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
+      <c r="J6" s="34" t="n"/>
       <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="34" t="n"/>
-      <c r="P6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -1113,13 +999,8 @@
       <c r="G7" s="24" t="n"/>
       <c r="H7" s="24" t="n"/>
       <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
-      <c r="O7" s="34" t="n"/>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1159,33 +1040,8 @@
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr">
-        <is>
-          <t>WorkSpeedTable.WorkSpeedTID</t>
-        </is>
-      </c>
-      <c r="K8" s="25" t="inlineStr">
-        <is>
-          <t>WorkSpeedTable.WorkSpeedTID</t>
-        </is>
-      </c>
-      <c r="L8" s="25" t="inlineStr">
-        <is>
-          <t>WorkSpeedTable.WorkSpeedTID</t>
-        </is>
-      </c>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t>WorkSpeedTable.WorkSpeedTID</t>
-        </is>
-      </c>
-      <c r="N8" s="25" t="inlineStr">
-        <is>
-          <t>WorkSpeedTable.WorkSpeedTID</t>
-        </is>
-      </c>
-      <c r="O8" s="34" t="n"/>
-      <c r="P8" s="25" t="n"/>
+      <c r="J8" s="34" t="n"/>
+      <c r="K8" s="25" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="32" t="n"/>
@@ -1229,37 +1085,12 @@
           <t>Hunting</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
-        <is>
-          <t>FarmingCap</t>
+      <c r="J9" s="35" t="inlineStr">
+        <is>
+          <t>BasePrice</t>
         </is>
       </c>
       <c r="K9" s="26" t="inlineStr">
-        <is>
-          <t>FishingCap</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="inlineStr">
-        <is>
-          <t>MiningCap</t>
-        </is>
-      </c>
-      <c r="M9" s="26" t="inlineStr">
-        <is>
-          <t>LoggingCap</t>
-        </is>
-      </c>
-      <c r="N9" s="26" t="inlineStr">
-        <is>
-          <t>HuntingCap</t>
-        </is>
-      </c>
-      <c r="O9" s="35" t="inlineStr">
-        <is>
-          <t>BasePrice</t>
-        </is>
-      </c>
-      <c r="P9" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1296,24 +1127,9 @@
         <v>1</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="P10" s="28" t="inlineStr">
+      <c r="K10" s="28" t="inlineStr">
         <is>
           <t>시작 지급. 전 산업 1 — 어떤 산업이든 시작할 수 있어야 한다</t>
         </is>
@@ -1350,24 +1166,9 @@
         <v>0</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P11" s="28" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t>농사 담당</t>
         </is>
@@ -1404,24 +1205,9 @@
         <v>2</v>
       </c>
       <c r="J12" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P12" s="28" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
@@ -1458,24 +1244,9 @@
         <v>1</v>
       </c>
       <c r="J13" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P13" s="28" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>채굴 담당</t>
         </is>
@@ -1512,24 +1283,9 @@
         <v>0</v>
       </c>
       <c r="J14" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P14" s="28" t="inlineStr">
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
@@ -1566,24 +1322,9 @@
         <v>3</v>
       </c>
       <c r="J15" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N15" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P15" s="28" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1620,24 +1361,9 @@
         <v>0</v>
       </c>
       <c r="J16" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="P16" s="28" t="inlineStr">
+      <c r="K16" s="28" t="inlineStr">
         <is>
           <t>농사 입문</t>
         </is>
@@ -1674,24 +1400,9 @@
         <v>1</v>
       </c>
       <c r="J17" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="P17" s="28" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t>낚시 입문</t>
         </is>
@@ -1728,24 +1439,9 @@
         <v>1</v>
       </c>
       <c r="J18" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="P18" s="28" t="inlineStr">
+      <c r="K18" s="28" t="inlineStr">
         <is>
           <t>채굴 입문</t>
         </is>
@@ -1782,24 +1478,9 @@
         <v>0</v>
       </c>
       <c r="J19" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="P19" s="28" t="inlineStr">
+      <c r="K19" s="28" t="inlineStr">
         <is>
           <t>벌목 입문</t>
         </is>
@@ -1836,24 +1517,9 @@
         <v>2</v>
       </c>
       <c r="J20" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="P20" s="28" t="inlineStr">
+      <c r="K20" s="28" t="inlineStr">
         <is>
           <t>사냥 입문</t>
         </is>
@@ -1890,24 +1556,9 @@
         <v>1</v>
       </c>
       <c r="J21" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P21" s="28" t="inlineStr">
+      <c r="K21" s="28" t="inlineStr">
         <is>
           <t>낚시 담당</t>
         </is>
@@ -1944,24 +1595,9 @@
         <v>4</v>
       </c>
       <c r="J22" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O22" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P22" s="28" t="inlineStr">
+      <c r="K22" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1998,24 +1634,9 @@
         <v>1</v>
       </c>
       <c r="J23" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K23" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="P23" s="28" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr">
         <is>
           <t>벌목 담당</t>
         </is>
@@ -2052,24 +1673,9 @@
         <v>1</v>
       </c>
       <c r="J24" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L24" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N24" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O24" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P24" s="28" t="inlineStr">
+      <c r="K24" s="28" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
@@ -2106,24 +1712,9 @@
         <v>0</v>
       </c>
       <c r="J25" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K25" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N25" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O25" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P25" s="28" t="inlineStr">
+      <c r="K25" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -2160,24 +1751,9 @@
         <v>2</v>
       </c>
       <c r="J26" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K26" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L26" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N26" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O26" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P26" s="28" t="inlineStr">
+      <c r="K26" s="28" t="inlineStr">
         <is>
           <t>채굴 특화</t>
         </is>
@@ -2214,24 +1790,9 @@
         <v>1</v>
       </c>
       <c r="J27" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N27" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P27" s="28" t="inlineStr">
+      <c r="K27" s="28" t="inlineStr">
         <is>
           <t>벌목 특화</t>
         </is>
@@ -2268,24 +1829,9 @@
         <v>5</v>
       </c>
       <c r="J28" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K28" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L28" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M28" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N28" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O28" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P28" s="28" t="inlineStr">
+      <c r="K28" s="28" t="inlineStr">
         <is>
           <t>사냥 특화</t>
         </is>
@@ -2322,24 +1868,9 @@
         <v>0</v>
       </c>
       <c r="J29" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K29" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M29" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N29" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O29" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P29" s="28" t="inlineStr">
+      <c r="K29" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -2376,24 +1907,9 @@
         <v>1</v>
       </c>
       <c r="J30" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K30" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M30" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="N30" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="O30" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="P30" s="28" t="inlineStr">
+      <c r="K30" s="28" t="inlineStr">
         <is>
           <t>낚시 특화</t>
         </is>
@@ -2430,24 +1946,9 @@
         <v>2</v>
       </c>
       <c r="J31" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L31" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M31" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N31" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O31" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="P31" s="28" t="inlineStr">
+      <c r="K31" s="28" t="inlineStr">
         <is>
           <t>채굴 정예</t>
         </is>
@@ -2484,24 +1985,9 @@
         <v>1</v>
       </c>
       <c r="J32" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K32" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L32" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M32" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N32" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O32" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="P32" s="28" t="inlineStr">
+      <c r="K32" s="28" t="inlineStr">
         <is>
           <t>낚시 정예</t>
         </is>
@@ -2538,24 +2024,9 @@
         <v>1</v>
       </c>
       <c r="J33" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K33" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N33" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O33" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="P33" s="28" t="inlineStr">
+      <c r="K33" s="28" t="inlineStr">
         <is>
           <t>농사 정예</t>
         </is>
@@ -2592,24 +2063,9 @@
         <v>7</v>
       </c>
       <c r="J34" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K34" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L34" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M34" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N34" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O34" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="P34" s="28" t="inlineStr">
+      <c r="K34" s="28" t="inlineStr">
         <is>
           <t>사냥 정예</t>
         </is>
@@ -2646,24 +2102,9 @@
         <v>1</v>
       </c>
       <c r="J35" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K35" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M35" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N35" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O35" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="P35" s="28" t="inlineStr">
+      <c r="K35" s="28" t="inlineStr">
         <is>
           <t>벌목 정예</t>
         </is>
@@ -2700,24 +2141,9 @@
         <v>2</v>
       </c>
       <c r="J36" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="L36" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="N36" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="O36" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="P36" s="28" t="inlineStr">
+      <c r="K36" s="28" t="inlineStr">
         <is>
           <t>농사 최상위</t>
         </is>
@@ -2754,24 +2180,9 @@
         <v>3</v>
       </c>
       <c r="J37" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="L37" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="M37" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="N37" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="O37" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="P37" s="28" t="inlineStr">
+      <c r="K37" s="28" t="inlineStr">
         <is>
           <t>낚시 최상위</t>
         </is>
@@ -2808,24 +2219,9 @@
         <v>2</v>
       </c>
       <c r="J38" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="L38" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="N38" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="O38" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="P38" s="28" t="inlineStr">
+      <c r="K38" s="28" t="inlineStr">
         <is>
           <t>채굴 최상위</t>
         </is>
@@ -2862,24 +2258,9 @@
         <v>7</v>
       </c>
       <c r="J39" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K39" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L39" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N39" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O39" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="P39" s="28" t="inlineStr">
+      <c r="K39" s="28" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
         </is>
@@ -3206,7 +2587,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="53" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3235,7 +2616,7 @@
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>적성 포인트</t>
+          <t>속도 가산(‰)</t>
         </is>
       </c>
       <c r="E2" s="23" t="inlineStr">
@@ -3355,7 +2736,7 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>AptitudePoint</t>
+          <t>SpeedAddPermille</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
@@ -3390,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
@@ -3407,7 +2788,7 @@
         <v>12</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
@@ -3424,7 +2805,7 @@
         <v>14</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E12" s="28" t="inlineStr">
         <is>
@@ -3441,7 +2822,7 @@
         <v>17</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
@@ -3458,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
@@ -3475,7 +2856,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
@@ -3492,7 +2873,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E16" s="28" t="inlineStr">
         <is>
@@ -3509,7 +2890,7 @@
         <v>35</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
@@ -3526,7 +2907,7 @@
         <v>42</v>
       </c>
       <c r="D18" s="27" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
@@ -3543,7 +2924,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
@@ -3560,7 +2941,7 @@
         <v>61</v>
       </c>
       <c r="D20" s="27" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E20" s="28" t="inlineStr">
         <is>
@@ -3577,7 +2958,7 @@
         <v>74</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
@@ -3594,7 +2975,7 @@
         <v>89</v>
       </c>
       <c r="D22" s="27" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
@@ -3611,7 +2992,7 @@
         <v>106</v>
       </c>
       <c r="D23" s="27" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
@@ -3628,7 +3009,7 @@
         <v>128</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
@@ -3645,7 +3026,7 @@
         <v>154</v>
       </c>
       <c r="D25" s="27" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
@@ -3662,7 +3043,7 @@
         <v>184</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E26" s="28" t="inlineStr">
         <is>
@@ -3679,7 +3060,7 @@
         <v>221</v>
       </c>
       <c r="D27" s="27" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
@@ -3696,7 +3077,7 @@
         <v>266</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
         <is>
@@ -3713,7 +3094,7 @@
         <v>319</v>
       </c>
       <c r="D29" s="27" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
@@ -3730,7 +3111,7 @@
         <v>383</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E30" s="28" t="inlineStr">
         <is>
@@ -3747,7 +3128,7 @@
         <v>460</v>
       </c>
       <c r="D31" s="27" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
@@ -3764,7 +3145,7 @@
         <v>552</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="E32" s="28" t="inlineStr">
         <is>
@@ -3781,7 +3162,7 @@
         <v>662</v>
       </c>
       <c r="D33" s="27" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E33" s="28" t="inlineStr">
         <is>
@@ -3798,7 +3179,7 @@
         <v>794</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="E34" s="28" t="inlineStr">
         <is>
@@ -3815,7 +3196,7 @@
         <v>953</v>
       </c>
       <c r="D35" s="27" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="E35" s="28" t="inlineStr">
         <is>
@@ -3832,7 +3213,7 @@
         <v>1144</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E36" s="28" t="inlineStr">
         <is>
@@ -3849,7 +3230,7 @@
         <v>1373</v>
       </c>
       <c r="D37" s="27" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="E37" s="28" t="inlineStr">
         <is>
@@ -3866,7 +3247,7 @@
         <v>1648</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="E38" s="28" t="inlineStr">
         <is>
@@ -3883,7 +3264,7 @@
         <v>1978</v>
       </c>
       <c r="D39" s="27" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E39" s="28" t="inlineStr">
         <is>
@@ -3900,7 +3281,7 @@
         <v>2373</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="E40" s="28" t="inlineStr">
         <is>
@@ -3917,7 +3298,7 @@
         <v>2848</v>
       </c>
       <c r="D41" s="27" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E41" s="28" t="inlineStr">
         <is>
@@ -3934,7 +3315,7 @@
         <v>3418</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E42" s="28" t="inlineStr">
         <is>
@@ -3951,7 +3332,7 @@
         <v>4101</v>
       </c>
       <c r="D43" s="27" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E43" s="28" t="inlineStr">
         <is>
@@ -3968,7 +3349,7 @@
         <v>4922</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="E44" s="28" t="inlineStr">
         <is>
@@ -3985,7 +3366,7 @@
         <v>5906</v>
       </c>
       <c r="D45" s="27" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E45" s="28" t="inlineStr">
         <is>
@@ -4002,7 +3383,7 @@
         <v>7088</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="E46" s="28" t="inlineStr">
         <is>
@@ -4019,7 +3400,7 @@
         <v>8505</v>
       </c>
       <c r="D47" s="27" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="E47" s="28" t="inlineStr">
         <is>
@@ -4036,7 +3417,7 @@
         <v>10206</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>1</v>
+        <v>390</v>
       </c>
       <c r="E48" s="28" t="inlineStr">
         <is>
@@ -4053,7 +3434,7 @@
         <v>12248</v>
       </c>
       <c r="D49" s="27" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E49" s="28" t="inlineStr">
         <is>
@@ -4070,7 +3451,7 @@
         <v>14697</v>
       </c>
       <c r="D50" s="27" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="E50" s="28" t="inlineStr">
         <is>
@@ -4087,7 +3468,7 @@
         <v>17637</v>
       </c>
       <c r="D51" s="27" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="E51" s="28" t="inlineStr">
         <is>
@@ -4104,7 +3485,7 @@
         <v>21164</v>
       </c>
       <c r="D52" s="27" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="E52" s="28" t="inlineStr">
         <is>
@@ -4121,7 +3502,7 @@
         <v>25397</v>
       </c>
       <c r="D53" s="27" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="E53" s="28" t="inlineStr">
         <is>
@@ -4138,7 +3519,7 @@
         <v>30477</v>
       </c>
       <c r="D54" s="27" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
@@ -4155,7 +3536,7 @@
         <v>36572</v>
       </c>
       <c r="D55" s="27" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
@@ -4172,7 +3553,7 @@
         <v>43887</v>
       </c>
       <c r="D56" s="27" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
@@ -4189,7 +3570,7 @@
         <v>52664</v>
       </c>
       <c r="D57" s="27" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="E57" s="28" t="inlineStr">
         <is>
@@ -4206,7 +3587,7 @@
         <v>63197</v>
       </c>
       <c r="D58" s="27" t="n">
-        <v>1</v>
+        <v>490</v>
       </c>
       <c r="E58" s="28" t="inlineStr">
         <is>
@@ -4223,7 +3604,7 @@
         <v>75836</v>
       </c>
       <c r="D59" s="27" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E59" s="28" t="inlineStr">
         <is>
@@ -4240,7 +3621,7 @@
         <v>91004</v>
       </c>
       <c r="D60" s="27" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="E60" s="28" t="inlineStr">
         <is>
@@ -4257,7 +3638,7 @@
         <v>109205</v>
       </c>
       <c r="D61" s="27" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="E61" s="28" t="inlineStr">
         <is>
@@ -4274,7 +3655,7 @@
         <v>131046</v>
       </c>
       <c r="D62" s="27" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="E62" s="28" t="inlineStr">
         <is>
@@ -4291,7 +3672,7 @@
         <v>157255</v>
       </c>
       <c r="D63" s="27" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="E63" s="28" t="inlineStr">
         <is>
@@ -4308,7 +3689,7 @@
         <v>188706</v>
       </c>
       <c r="D64" s="27" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="E64" s="28" t="inlineStr">
         <is>
@@ -4325,7 +3706,7 @@
         <v>226448</v>
       </c>
       <c r="D65" s="27" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="E65" s="28" t="inlineStr">
         <is>
@@ -4342,7 +3723,7 @@
         <v>271737</v>
       </c>
       <c r="D66" s="27" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="E66" s="28" t="inlineStr">
         <is>
@@ -4359,7 +3740,7 @@
         <v>326085</v>
       </c>
       <c r="D67" s="27" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="E67" s="28" t="inlineStr">
         <is>
@@ -4376,7 +3757,7 @@
         <v>391302</v>
       </c>
       <c r="D68" s="27" t="n">
-        <v>1</v>
+        <v>590</v>
       </c>
       <c r="E68" s="28" t="inlineStr">
         <is>
@@ -4393,7 +3774,7 @@
         <v>469562</v>
       </c>
       <c r="D69" s="27" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E69" s="28" t="inlineStr">
         <is>
@@ -4410,7 +3791,7 @@
         <v>563475</v>
       </c>
       <c r="D70" s="27" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="E70" s="28" t="inlineStr">
         <is>
@@ -4427,7 +3808,7 @@
         <v>676170</v>
       </c>
       <c r="D71" s="27" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="E71" s="28" t="inlineStr">
         <is>
@@ -4444,7 +3825,7 @@
         <v>811404</v>
       </c>
       <c r="D72" s="27" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="E72" s="28" t="inlineStr">
         <is>
@@ -4461,7 +3842,7 @@
         <v>973685</v>
       </c>
       <c r="D73" s="27" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="E73" s="28" t="inlineStr">
         <is>
@@ -4478,7 +3859,7 @@
         <v>1168422</v>
       </c>
       <c r="D74" s="27" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="E74" s="28" t="inlineStr">
         <is>
@@ -4495,7 +3876,7 @@
         <v>1402106</v>
       </c>
       <c r="D75" s="27" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="E75" s="28" t="inlineStr">
         <is>
@@ -4512,7 +3893,7 @@
         <v>1682527</v>
       </c>
       <c r="D76" s="27" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="E76" s="28" t="inlineStr">
         <is>
@@ -4529,7 +3910,7 @@
         <v>2019033</v>
       </c>
       <c r="D77" s="27" t="n">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="E77" s="28" t="inlineStr">
         <is>
@@ -4546,7 +3927,7 @@
         <v>2422839</v>
       </c>
       <c r="D78" s="27" t="n">
-        <v>1</v>
+        <v>690</v>
       </c>
       <c r="E78" s="28" t="inlineStr">
         <is>
@@ -4563,7 +3944,7 @@
         <v>2907407</v>
       </c>
       <c r="D79" s="27" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E79" s="28" t="inlineStr">
         <is>
@@ -4580,7 +3961,7 @@
         <v>3488889</v>
       </c>
       <c r="D80" s="27" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="E80" s="28" t="inlineStr">
         <is>
@@ -4597,7 +3978,7 @@
         <v>4186667</v>
       </c>
       <c r="D81" s="27" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E81" s="28" t="inlineStr">
         <is>
@@ -4614,7 +3995,7 @@
         <v>5024000</v>
       </c>
       <c r="D82" s="27" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="E82" s="28" t="inlineStr">
         <is>
@@ -4631,7 +4012,7 @@
         <v>6028801</v>
       </c>
       <c r="D83" s="27" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="E83" s="28" t="inlineStr">
         <is>
@@ -4648,7 +4029,7 @@
         <v>7234561</v>
       </c>
       <c r="D84" s="27" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="E84" s="28" t="inlineStr">
         <is>
@@ -4665,7 +4046,7 @@
         <v>8681473</v>
       </c>
       <c r="D85" s="27" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="E85" s="28" t="inlineStr">
         <is>
@@ -4682,7 +4063,7 @@
         <v>10417768</v>
       </c>
       <c r="D86" s="27" t="n">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="E86" s="28" t="inlineStr">
         <is>
@@ -4699,7 +4080,7 @@
         <v>12501322</v>
       </c>
       <c r="D87" s="27" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="E87" s="28" t="inlineStr">
         <is>
@@ -4716,7 +4097,7 @@
         <v>15001586</v>
       </c>
       <c r="D88" s="27" t="n">
-        <v>1</v>
+        <v>790</v>
       </c>
       <c r="E88" s="28" t="inlineStr">
         <is>
@@ -4733,7 +4114,7 @@
         <v>18001903</v>
       </c>
       <c r="D89" s="27" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E89" s="28" t="inlineStr">
         <is>
@@ -4750,7 +4131,7 @@
         <v>21602284</v>
       </c>
       <c r="D90" s="27" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="E90" s="28" t="inlineStr">
         <is>
@@ -4767,7 +4148,7 @@
         <v>25922741</v>
       </c>
       <c r="D91" s="27" t="n">
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="E91" s="28" t="inlineStr">
         <is>
@@ -4784,7 +4165,7 @@
         <v>31107289</v>
       </c>
       <c r="D92" s="27" t="n">
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="E92" s="28" t="inlineStr">
         <is>
@@ -4801,7 +4182,7 @@
         <v>37328747</v>
       </c>
       <c r="D93" s="27" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="E93" s="28" t="inlineStr">
         <is>
@@ -4818,7 +4199,7 @@
         <v>44794497</v>
       </c>
       <c r="D94" s="27" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="E94" s="28" t="inlineStr">
         <is>
@@ -4835,7 +4216,7 @@
         <v>53753396</v>
       </c>
       <c r="D95" s="27" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="E95" s="28" t="inlineStr">
         <is>
@@ -4852,7 +4233,7 @@
         <v>64504076</v>
       </c>
       <c r="D96" s="27" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="E96" s="28" t="inlineStr">
         <is>
@@ -4869,7 +4250,7 @@
         <v>77404891</v>
       </c>
       <c r="D97" s="27" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="E97" s="28" t="inlineStr">
         <is>
@@ -4886,7 +4267,7 @@
         <v>92885869</v>
       </c>
       <c r="D98" s="27" t="n">
-        <v>1</v>
+        <v>890</v>
       </c>
       <c r="E98" s="28" t="inlineStr">
         <is>
@@ -4903,7 +4284,7 @@
         <v>111463043</v>
       </c>
       <c r="D99" s="27" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E99" s="28" t="inlineStr">
         <is>
@@ -4920,7 +4301,7 @@
         <v>133755652</v>
       </c>
       <c r="D100" s="27" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="E100" s="28" t="inlineStr">
         <is>
@@ -4937,7 +4318,7 @@
         <v>160506782</v>
       </c>
       <c r="D101" s="27" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="E101" s="28" t="inlineStr">
         <is>
@@ -4954,7 +4335,7 @@
         <v>192608139</v>
       </c>
       <c r="D102" s="27" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="E102" s="28" t="inlineStr">
         <is>
@@ -4971,7 +4352,7 @@
         <v>231129767</v>
       </c>
       <c r="D103" s="27" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="E103" s="28" t="inlineStr">
         <is>
@@ -4988,7 +4369,7 @@
         <v>277355721</v>
       </c>
       <c r="D104" s="27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="E104" s="28" t="inlineStr">
         <is>
@@ -5005,7 +4386,7 @@
         <v>332826865</v>
       </c>
       <c r="D105" s="27" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="E105" s="28" t="inlineStr">
         <is>
@@ -5022,7 +4403,7 @@
         <v>399392238</v>
       </c>
       <c r="D106" s="27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="E106" s="28" t="inlineStr">
         <is>
@@ -5039,7 +4420,7 @@
         <v>479270685</v>
       </c>
       <c r="D107" s="27" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="E107" s="28" t="inlineStr">
         <is>
@@ -5056,7 +4437,7 @@
         <v>575124823</v>
       </c>
       <c r="D108" s="27" t="n">
-        <v>1</v>
+        <v>990</v>
       </c>
       <c r="E108" s="28" t="inlineStr">
         <is>

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -9,6 +9,7 @@
     <sheet name="CharacterTable" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WorkSpeedTable" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CharacterLevelTable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CharacterStarTable" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -210,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -312,6 +313,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4449,4 +4453,247 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>별</t>
+        </is>
+      </c>
+      <c r="C2" s="33" t="inlineStr">
+        <is>
+          <t>필요 재료</t>
+        </is>
+      </c>
+      <c r="D2" s="33" t="inlineStr">
+        <is>
+          <t>속도 가산(‰)</t>
+        </is>
+      </c>
+      <c r="E2" s="33" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="34" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="n"/>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>CharacterStarTID</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>RequiredCount</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>SpeedAddPermille</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>★1 — 누적 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>★2 — 누적 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>★3 — 누적 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>★4 — 누적 76 · 최대</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>낚시 적성</t>
+          <t>발굴 적성</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F9" s="26" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G9" s="26" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K12" s="28" t="inlineStr">
         <is>
-          <t>낚시 담당</t>
+          <t>발굴 담당</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="K17" s="28" t="inlineStr">
         <is>
-          <t>낚시 입문</t>
+          <t>발굴 입문</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K21" s="28" t="inlineStr">
         <is>
-          <t>낚시 담당</t>
+          <t>발굴 담당</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="K24" s="28" t="inlineStr">
         <is>
-          <t>낚시 특화</t>
+          <t>발굴 특화</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="K30" s="28" t="inlineStr">
         <is>
-          <t>낚시 특화</t>
+          <t>발굴 특화</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="K32" s="28" t="inlineStr">
         <is>
-          <t>낚시 정예</t>
+          <t>발굴 정예</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="K37" s="28" t="inlineStr">
         <is>
-          <t>낚시 최상위</t>
+          <t>발굴 최상위</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -743,7 +743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -909,7 +909,7 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
@@ -2272,12 +2272,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2575,12 +2575,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4451,7 +4451,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -743,7 +743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -751,10 +751,10 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15" bestFit="1" customWidth="1" min="4" max="8"/>
+    <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>램볼</t>
+          <t>떠돌이 전사</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>치키피</t>
+          <t>숲 슬라임</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>펭구렛</t>
+          <t>뿔쥐</t>
         </is>
       </c>
       <c r="D12" s="28" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>캐티바</t>
+          <t>가시 슬라임</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>리프몽</t>
+          <t>방랑 기사</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>폭스파크스</t>
+          <t>날개 눈알</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>밀개비</t>
+          <t>들쥐</t>
         </is>
       </c>
       <c r="D16" s="28" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>두더삽</t>
+          <t>동굴 박쥐</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>살쾡이</t>
+          <t>흡혈 박쥐</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>갈대오리</t>
+          <t>망령 마법사</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>뿔사슴이</t>
+          <t>화염 마법사</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>해달수</t>
+          <t>미믹</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>흙두꺼비</t>
+          <t>버섯 인간</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>광부오소리</t>
+          <t>고블린</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>도끼늑대</t>
+          <t>은빛 기사</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>창날매</t>
+          <t>그림자 마법사</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>이삭토끼</t>
+          <t>무예가</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>산호게</t>
+          <t>해골 병사</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>화산도롱뇽</t>
+          <t>바위 골렘</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>파도고래</t>
+          <t>붉은 집게게</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>대지곰</t>
+          <t>대검 전사</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>강철사마귀</t>
+          <t>검왕</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>거목정령</t>
+          <t>영웅 기사</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>황금기린</t>
+          <t>죽음의 사신</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>심연이무기</t>
+          <t>흑기사</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>별빛드래곤</t>
+          <t>질풍 검호</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -2272,12 +2272,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2575,12 +2575,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4451,7 +4451,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -404,7 +404,7 @@
         <t>레어도 (전역 등급)</t>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>사냥 적성(전투력)</t>
       </text>
@@ -748,21 +748,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
@@ -781,6 +781,7 @@
       <c r="I1" s="30" t="n"/>
       <c r="J1" s="30" t="n"/>
       <c r="K1" s="30" t="n"/>
+      <c r="L1" s="30" t="n"/>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
@@ -805,35 +806,40 @@
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
+          <t>종족</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
           <t>농사 적성</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>발굴 적성</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>채굴 적성</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>벌목 적성</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="J2" s="23" t="inlineStr">
         <is>
           <t>사냥 적성</t>
         </is>
       </c>
-      <c r="J2" s="33" t="inlineStr">
+      <c r="K2" s="33" t="inlineStr">
         <is>
           <t>기본 가격</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="L2" s="23" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -885,12 +891,17 @@
           <t>a</t>
         </is>
       </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -919,35 +930,40 @@
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
+          <t>eCharacterRace</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="K4" s="34" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -967,10 +983,11 @@
       <c r="G5" s="24" t="n"/>
       <c r="H5" s="24" t="n"/>
       <c r="I5" s="24" t="n"/>
-      <c r="J5" s="34" t="n">
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -986,8 +1003,9 @@
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
       <c r="I6" s="24" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="34" t="n"/>
+      <c r="L6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -1003,8 +1021,9 @@
       <c r="G7" s="24" t="n"/>
       <c r="H7" s="24" t="n"/>
       <c r="I7" s="24" t="n"/>
-      <c r="J7" s="34" t="n"/>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1019,33 +1038,34 @@
       <c r="B8" s="25" t="n"/>
       <c r="C8" s="25" t="n"/>
       <c r="D8" s="25" t="n"/>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>WorkSpeedTable.WorkSpeedTID</t>
         </is>
       </c>
-      <c r="J8" s="34" t="n"/>
-      <c r="K8" s="25" t="n"/>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="25" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="32" t="n"/>
@@ -1066,35 +1086,40 @@
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
           <t>Farming</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>Excavation</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>Hunting</t>
         </is>
       </c>
-      <c r="J9" s="35" t="inlineStr">
+      <c r="K9" s="35" t="inlineStr">
         <is>
           <t>BasePrice</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="L9" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1115,8 +1140,10 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E10" s="27" t="n">
-        <v>1</v>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F10" s="27" t="n">
         <v>1</v>
@@ -1131,9 +1158,12 @@
         <v>1</v>
       </c>
       <c r="J10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="L10" s="28" t="inlineStr">
         <is>
           <t>시작 지급. 전 산업 1 — 어떤 산업이든 시작할 수 있어야 한다</t>
         </is>
@@ -1154,25 +1184,30 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="G11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="J11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="27" t="n">
+      <c r="K11" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>농사 담당</t>
         </is>
@@ -1193,11 +1228,13 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E12" s="27" t="n">
-        <v>1</v>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="27" t="n">
         <v>0</v>
@@ -1206,14 +1243,17 @@
         <v>0</v>
       </c>
       <c r="I12" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="K12" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K12" s="28" t="inlineStr">
-        <is>
-          <t>발굴 담당</t>
+      <c r="L12" s="28" t="inlineStr">
+        <is>
+          <t>벌목 담당</t>
         </is>
       </c>
     </row>
@@ -1232,25 +1272,30 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="G13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="H13" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K13" s="28" t="inlineStr">
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>채굴 담당</t>
         </is>
@@ -1271,27 +1316,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
-        <v>1</v>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F14" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="27" t="n">
         <v>0</v>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>3</v>
       </c>
       <c r="I14" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K14" s="28" t="inlineStr">
-        <is>
-          <t>벌목 담당</t>
+      <c r="L14" s="28" t="inlineStr">
+        <is>
+          <t>사냥 담당</t>
         </is>
       </c>
     </row>
@@ -1310,25 +1360,30 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="G15" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="27" t="n">
+      <c r="J15" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="27" t="n">
+      <c r="K15" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1349,25 +1404,30 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="G16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="27" t="n">
+      <c r="K16" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="K16" s="28" t="inlineStr">
+      <c r="L16" s="28" t="inlineStr">
         <is>
           <t>농사 입문</t>
         </is>
@@ -1380,7 +1440,7 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>물방개미</t>
+          <t>견습 발굴꾼</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">
@@ -1388,27 +1448,32 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="G17" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="K17" s="28" t="inlineStr">
-        <is>
-          <t>발굴 입문</t>
+      <c r="L17" s="28" t="inlineStr">
+        <is>
+          <t>발굴 입문 — 그림 없음, 기본 캐릭터 임시</t>
         </is>
       </c>
     </row>
@@ -1427,25 +1492,30 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
-        <v>0</v>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="F18" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="I18" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="K18" s="28" t="inlineStr">
+      <c r="L18" s="28" t="inlineStr">
         <is>
           <t>채굴 입문</t>
         </is>
@@ -1458,7 +1528,7 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>톱니쥐</t>
+          <t>견습 나무꾼</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -1466,27 +1536,32 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E19" s="27" t="n">
-        <v>1</v>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="27" t="n">
+      <c r="J19" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="27" t="n">
+      <c r="K19" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="K19" s="28" t="inlineStr">
-        <is>
-          <t>벌목 입문</t>
+      <c r="L19" s="28" t="inlineStr">
+        <is>
+          <t>벌목 입문 — 그림 없음, 기본 캐릭터 임시</t>
         </is>
       </c>
     </row>
@@ -1505,25 +1580,30 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="G20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="I20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="27" t="n">
+      <c r="K20" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="K20" s="28" t="inlineStr">
+      <c r="L20" s="28" t="inlineStr">
         <is>
           <t>사냥 입문</t>
         </is>
@@ -1544,27 +1624,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E21" s="27" t="n">
-        <v>1</v>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
       </c>
       <c r="F21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="27" t="n">
+      <c r="K21" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K21" s="28" t="inlineStr">
-        <is>
-          <t>발굴 담당</t>
+      <c r="L21" s="28" t="inlineStr">
+        <is>
+          <t>사냥 담당</t>
         </is>
       </c>
     </row>
@@ -1583,25 +1668,30 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E22" s="27" t="n">
-        <v>1</v>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H22" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="27" t="n">
+      <c r="K22" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K22" s="28" t="inlineStr">
+      <c r="L22" s="28" t="inlineStr">
         <is>
           <t>사냥 담당</t>
         </is>
@@ -1614,7 +1704,7 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>솔방울곰</t>
+          <t>나무꾼</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -1622,27 +1712,32 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="E23" s="27" t="n">
-        <v>1</v>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="J23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="K23" s="28" t="inlineStr">
-        <is>
-          <t>벌목 담당</t>
+      <c r="L23" s="28" t="inlineStr">
+        <is>
+          <t>벌목 담당 — 그림 없음, 기본 캐릭터 임시</t>
         </is>
       </c>
     </row>
@@ -1661,25 +1756,30 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E24" s="27" t="n">
-        <v>1</v>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="F24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="H24" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="I24" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K24" s="28" t="inlineStr">
+      <c r="L24" s="28" t="inlineStr">
         <is>
           <t>발굴 특화</t>
         </is>
@@ -1700,25 +1800,30 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="G25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="27" t="n">
         <v>2</v>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>0</v>
       </c>
       <c r="I25" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K25" s="28" t="inlineStr">
+      <c r="L25" s="28" t="inlineStr">
         <is>
           <t>농사 특화</t>
         </is>
@@ -1739,25 +1844,30 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E26" s="27" t="n">
-        <v>0</v>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="F26" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="27" t="n">
         <v>5</v>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>2</v>
       </c>
       <c r="I26" s="27" t="n">
         <v>2</v>
       </c>
       <c r="J26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K26" s="28" t="inlineStr">
+      <c r="L26" s="28" t="inlineStr">
         <is>
           <t>채굴 특화</t>
         </is>
@@ -1778,27 +1888,32 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E27" s="27" t="n">
-        <v>1</v>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="H27" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="I27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="27" t="n">
+      <c r="K27" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K27" s="28" t="inlineStr">
-        <is>
-          <t>벌목 특화</t>
+      <c r="L27" s="28" t="inlineStr">
+        <is>
+          <t>사냥 특화</t>
         </is>
       </c>
     </row>
@@ -1817,25 +1932,30 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="G28" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="H28" s="27" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="27" t="n">
+      <c r="K28" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="L28" s="28" t="inlineStr">
         <is>
           <t>사냥 특화</t>
         </is>
@@ -1856,27 +1976,32 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="n">
+      <c r="K29" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K29" s="28" t="inlineStr">
-        <is>
-          <t>농사 특화</t>
+      <c r="L29" s="28" t="inlineStr">
+        <is>
+          <t>사냥 특화</t>
         </is>
       </c>
     </row>
@@ -1895,25 +2020,30 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="E30" s="27" t="n">
-        <v>1</v>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
       </c>
       <c r="F30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="H30" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="I30" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="J30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="K30" s="28" t="inlineStr">
+      <c r="L30" s="28" t="inlineStr">
         <is>
           <t>발굴 특화</t>
         </is>
@@ -1934,25 +2064,30 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E31" s="27" t="n">
-        <v>1</v>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>Golem</t>
+        </is>
       </c>
       <c r="F31" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="27" t="n">
+      <c r="H31" s="27" t="n">
         <v>7</v>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>2</v>
       </c>
       <c r="I31" s="27" t="n">
         <v>2</v>
       </c>
       <c r="J31" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="K31" s="28" t="inlineStr">
+      <c r="L31" s="28" t="inlineStr">
         <is>
           <t>채굴 정예</t>
         </is>
@@ -1973,27 +2108,32 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="27" t="n">
+      <c r="G32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="J32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="K32" s="28" t="inlineStr">
-        <is>
-          <t>발굴 정예</t>
+      <c r="L32" s="28" t="inlineStr">
+        <is>
+          <t>벌목 정예</t>
         </is>
       </c>
     </row>
@@ -2012,27 +2152,32 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
-        <v>7</v>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F33" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="27" t="n">
         <v>2</v>
       </c>
       <c r="I33" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="K33" s="28" t="inlineStr">
-        <is>
-          <t>농사 정예</t>
+      <c r="L33" s="28" t="inlineStr">
+        <is>
+          <t>사냥 정예</t>
         </is>
       </c>
     </row>
@@ -2051,25 +2196,30 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E34" s="27" t="n">
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="27" t="n">
+      <c r="G34" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="H34" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="27" t="n">
+      <c r="I34" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="27" t="n">
+      <c r="J34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J34" s="27" t="n">
+      <c r="K34" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="K34" s="28" t="inlineStr">
+      <c r="L34" s="28" t="inlineStr">
         <is>
           <t>사냥 정예</t>
         </is>
@@ -2090,27 +2240,32 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="27" t="n">
-        <v>1</v>
-      </c>
       <c r="G35" s="27" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="27" t="n">
+      <c r="K35" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="K35" s="28" t="inlineStr">
-        <is>
-          <t>벌목 정예</t>
+      <c r="L35" s="28" t="inlineStr">
+        <is>
+          <t>사냥 정예</t>
         </is>
       </c>
     </row>
@@ -2129,25 +2284,30 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
         <v>9</v>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>2</v>
       </c>
       <c r="G36" s="27" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="27" t="n">
+      <c r="J36" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="27" t="n">
+      <c r="K36" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="K36" s="28" t="inlineStr">
+      <c r="L36" s="28" t="inlineStr">
         <is>
           <t>농사 최상위</t>
         </is>
@@ -2168,27 +2328,32 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E37" s="27" t="n">
-        <v>1</v>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G37" s="27" t="n">
         <v>3</v>
       </c>
       <c r="H37" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="K37" s="28" t="inlineStr">
-        <is>
-          <t>발굴 최상위</t>
+      <c r="L37" s="28" t="inlineStr">
+        <is>
+          <t>사냥 최상위</t>
         </is>
       </c>
     </row>
@@ -2207,25 +2372,30 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="E38" s="27" t="n">
-        <v>1</v>
+      <c r="E38" s="28" t="inlineStr">
+        <is>
+          <t>Golem</t>
+        </is>
       </c>
       <c r="F38" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="I38" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="I38" s="27" t="n">
+      <c r="J38" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="27" t="n">
+      <c r="K38" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="K38" s="28" t="inlineStr">
+      <c r="L38" s="28" t="inlineStr">
         <is>
           <t>채굴 최상위</t>
         </is>
@@ -2246,8 +2416,10 @@
           <t>Mythic</t>
         </is>
       </c>
-      <c r="E39" s="27" t="n">
-        <v>7</v>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
       </c>
       <c r="F39" s="27" t="n">
         <v>7</v>
@@ -2262,9 +2434,12 @@
         <v>7</v>
       </c>
       <c r="J39" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="K39" s="28" t="inlineStr">
+      <c r="L39" s="28" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
         </is>

--- a/GameDesign/Excel/Character.xlsx
+++ b/GameDesign/Excel/Character.xlsx
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="L17" s="28" t="inlineStr">
         <is>
-          <t>발굴 입문 — 그림 없음, 기본 캐릭터 임시</t>
+          <t>발굴 입문 — 삽</t>
         </is>
       </c>
     </row>
@@ -2442,6 +2442,50 @@
       <c r="L39" s="28" t="inlineStr">
         <is>
           <t>만능형 — 전 산업 7. 단일 산업 최고는 전설 특화가 유지한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="n"/>
+      <c r="B40" s="27" t="n">
+        <v>1031</v>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>숙련 채굴꾼</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="L40" s="28" t="inlineStr">
+        <is>
+          <t>채굴 담당 — 견습 발굴꾼(1008)과 같은 생김새에 곡괭이</t>
         </is>
       </c>
     </row>
